--- a/storage/warehouse/noms/nomenclature_WB_2026-07-27_21-14.xlsx
+++ b/storage/warehouse/noms/nomenclature_WB_2026-07-27_21-14.xlsx
@@ -11,12 +11,12 @@
     <sheet name="Справочники" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="651">
   <si>
     <t>ID</t>
   </si>
@@ -1843,6 +1843,9 @@
   </si>
   <si>
     <t>XF6535H</t>
+  </si>
+  <si>
+    <t>Бескаркасные</t>
   </si>
   <si>
     <t>Колодки</t>
@@ -2324,33 +2327,33 @@
   <dimension ref="A1:AA493"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="42.418" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="65.984" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="232.229" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="5.856" customWidth="true" style="0"/>
+    <col min="2" max="2" width="26.993" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.569" customWidth="true" style="0"/>
+    <col min="4" max="4" width="42.418" customWidth="true" style="0"/>
+    <col min="5" max="5" width="8.141" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.711" customWidth="true" style="0"/>
+    <col min="7" max="7" width="8.141" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.997" customWidth="true" style="0"/>
+    <col min="9" max="9" width="10.569" customWidth="true" style="0"/>
+    <col min="10" max="10" width="65.984" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.71" customWidth="true" style="0"/>
+    <col min="12" max="12" width="24.708" customWidth="true" style="0"/>
+    <col min="13" max="13" width="16.425" customWidth="true" style="0"/>
+    <col min="14" max="14" width="11.711" customWidth="true" style="0"/>
+    <col min="15" max="15" width="15.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="30.564" customWidth="true" style="0"/>
+    <col min="17" max="17" width="28.136" customWidth="true" style="0"/>
+    <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
+    <col min="19" max="19" width="21.138" customWidth="true" style="0"/>
+    <col min="20" max="20" width="232.229" customWidth="true" style="0"/>
+    <col min="21" max="21" width="26.993" customWidth="true" style="0"/>
+    <col min="22" max="22" width="22.28" customWidth="true" style="0"/>
+    <col min="23" max="23" width="16.425" customWidth="true" style="0"/>
+    <col min="24" max="24" width="9.283" customWidth="true" style="0"/>
+    <col min="25" max="25" width="22.28" customWidth="true" style="0"/>
+    <col min="26" max="26" width="15.282" customWidth="true" style="0"/>
+    <col min="27" max="27" width="22.28" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
@@ -2476,6 +2479,9 @@
       <c r="M2" t="s">
         <v>35</v>
       </c>
+      <c r="N2" t="s">
+        <v>609</v>
+      </c>
       <c r="O2" t="s">
         <v>36</v>
       </c>
@@ -2547,6 +2553,9 @@
       <c r="M3" t="s">
         <v>35</v>
       </c>
+      <c r="N3" t="s">
+        <v>609</v>
+      </c>
       <c r="O3" t="s">
         <v>36</v>
       </c>
@@ -2618,6 +2627,9 @@
       <c r="M4" t="s">
         <v>35</v>
       </c>
+      <c r="N4" t="s">
+        <v>609</v>
+      </c>
       <c r="O4" t="s">
         <v>36</v>
       </c>
@@ -2689,6 +2701,9 @@
       <c r="M5" t="s">
         <v>35</v>
       </c>
+      <c r="N5" t="s">
+        <v>609</v>
+      </c>
       <c r="O5" t="s">
         <v>36</v>
       </c>
@@ -2760,6 +2775,9 @@
       <c r="M6" t="s">
         <v>46</v>
       </c>
+      <c r="N6" t="s">
+        <v>609</v>
+      </c>
       <c r="O6" t="s">
         <v>36</v>
       </c>
@@ -2831,6 +2849,9 @@
       <c r="M7" t="s">
         <v>46</v>
       </c>
+      <c r="N7" t="s">
+        <v>609</v>
+      </c>
       <c r="O7" t="s">
         <v>36</v>
       </c>
@@ -2902,6 +2923,9 @@
       <c r="M8" t="s">
         <v>46</v>
       </c>
+      <c r="N8" t="s">
+        <v>609</v>
+      </c>
       <c r="O8" t="s">
         <v>36</v>
       </c>
@@ -2973,6 +2997,9 @@
       <c r="M9" t="s">
         <v>46</v>
       </c>
+      <c r="N9" t="s">
+        <v>609</v>
+      </c>
       <c r="O9" t="s">
         <v>36</v>
       </c>
@@ -3044,6 +3071,9 @@
       <c r="M10" t="s">
         <v>35</v>
       </c>
+      <c r="N10" t="s">
+        <v>609</v>
+      </c>
       <c r="O10" t="s">
         <v>36</v>
       </c>
@@ -3118,6 +3148,9 @@
       <c r="M11" t="s">
         <v>35</v>
       </c>
+      <c r="N11" t="s">
+        <v>609</v>
+      </c>
       <c r="O11" t="s">
         <v>36</v>
       </c>
@@ -3192,6 +3225,9 @@
       <c r="M12" t="s">
         <v>35</v>
       </c>
+      <c r="N12" t="s">
+        <v>609</v>
+      </c>
       <c r="O12" t="s">
         <v>36</v>
       </c>
@@ -3266,6 +3302,9 @@
       <c r="M13" t="s">
         <v>35</v>
       </c>
+      <c r="N13" t="s">
+        <v>609</v>
+      </c>
       <c r="O13" t="s">
         <v>36</v>
       </c>
@@ -3340,6 +3379,9 @@
       <c r="M14" t="s">
         <v>35</v>
       </c>
+      <c r="N14" t="s">
+        <v>609</v>
+      </c>
       <c r="O14" t="s">
         <v>36</v>
       </c>
@@ -3414,6 +3456,9 @@
       <c r="M15" t="s">
         <v>35</v>
       </c>
+      <c r="N15" t="s">
+        <v>609</v>
+      </c>
       <c r="O15" t="s">
         <v>36</v>
       </c>
@@ -3488,6 +3533,9 @@
       <c r="M16" t="s">
         <v>35</v>
       </c>
+      <c r="N16" t="s">
+        <v>609</v>
+      </c>
       <c r="O16" t="s">
         <v>36</v>
       </c>
@@ -3562,6 +3610,9 @@
       <c r="M17" t="s">
         <v>35</v>
       </c>
+      <c r="N17" t="s">
+        <v>609</v>
+      </c>
       <c r="O17" t="s">
         <v>62</v>
       </c>
@@ -3633,6 +3684,9 @@
       <c r="M18" t="s">
         <v>35</v>
       </c>
+      <c r="N18" t="s">
+        <v>609</v>
+      </c>
       <c r="O18" t="s">
         <v>62</v>
       </c>
@@ -3704,6 +3758,9 @@
       <c r="M19" t="s">
         <v>46</v>
       </c>
+      <c r="N19" t="s">
+        <v>609</v>
+      </c>
       <c r="O19" t="s">
         <v>62</v>
       </c>
@@ -3775,6 +3832,9 @@
       <c r="M20" t="s">
         <v>35</v>
       </c>
+      <c r="N20" t="s">
+        <v>609</v>
+      </c>
       <c r="O20" t="s">
         <v>36</v>
       </c>
@@ -3849,6 +3909,9 @@
       <c r="M21" t="s">
         <v>35</v>
       </c>
+      <c r="N21" t="s">
+        <v>609</v>
+      </c>
       <c r="O21" t="s">
         <v>36</v>
       </c>
@@ -3923,6 +3986,9 @@
       <c r="M22" t="s">
         <v>35</v>
       </c>
+      <c r="N22" t="s">
+        <v>609</v>
+      </c>
       <c r="O22" t="s">
         <v>36</v>
       </c>
@@ -3997,6 +4063,9 @@
       <c r="M23" t="s">
         <v>35</v>
       </c>
+      <c r="N23" t="s">
+        <v>609</v>
+      </c>
       <c r="O23" t="s">
         <v>36</v>
       </c>
@@ -4071,6 +4140,9 @@
       <c r="M24" t="s">
         <v>35</v>
       </c>
+      <c r="N24" t="s">
+        <v>609</v>
+      </c>
       <c r="O24" t="s">
         <v>36</v>
       </c>
@@ -4145,6 +4217,9 @@
       <c r="M25" t="s">
         <v>35</v>
       </c>
+      <c r="N25" t="s">
+        <v>609</v>
+      </c>
       <c r="O25" t="s">
         <v>36</v>
       </c>
@@ -4219,6 +4294,9 @@
       <c r="M26" t="s">
         <v>35</v>
       </c>
+      <c r="N26" t="s">
+        <v>609</v>
+      </c>
       <c r="O26" t="s">
         <v>36</v>
       </c>
@@ -4293,6 +4371,9 @@
       <c r="M27" t="s">
         <v>35</v>
       </c>
+      <c r="N27" t="s">
+        <v>609</v>
+      </c>
       <c r="O27" t="s">
         <v>36</v>
       </c>
@@ -4367,6 +4448,9 @@
       <c r="M28" t="s">
         <v>35</v>
       </c>
+      <c r="N28" t="s">
+        <v>609</v>
+      </c>
       <c r="O28" t="s">
         <v>36</v>
       </c>
@@ -4441,6 +4525,9 @@
       <c r="M29" t="s">
         <v>35</v>
       </c>
+      <c r="N29" t="s">
+        <v>609</v>
+      </c>
       <c r="O29" t="s">
         <v>36</v>
       </c>
@@ -4515,6 +4602,9 @@
       <c r="M30" t="s">
         <v>85</v>
       </c>
+      <c r="N30" t="s">
+        <v>609</v>
+      </c>
       <c r="O30" t="s">
         <v>62</v>
       </c>
@@ -4586,6 +4676,9 @@
       <c r="M31" t="s">
         <v>35</v>
       </c>
+      <c r="N31" t="s">
+        <v>609</v>
+      </c>
       <c r="O31" t="s">
         <v>36</v>
       </c>
@@ -4660,6 +4753,9 @@
       <c r="M32" t="s">
         <v>35</v>
       </c>
+      <c r="N32" t="s">
+        <v>609</v>
+      </c>
       <c r="O32" t="s">
         <v>36</v>
       </c>
@@ -4734,6 +4830,9 @@
       <c r="M33" t="s">
         <v>35</v>
       </c>
+      <c r="N33" t="s">
+        <v>609</v>
+      </c>
       <c r="O33" t="s">
         <v>36</v>
       </c>
@@ -4808,6 +4907,9 @@
       <c r="M34" t="s">
         <v>35</v>
       </c>
+      <c r="N34" t="s">
+        <v>609</v>
+      </c>
       <c r="O34" t="s">
         <v>36</v>
       </c>
@@ -4882,6 +4984,9 @@
       <c r="M35" t="s">
         <v>35</v>
       </c>
+      <c r="N35" t="s">
+        <v>609</v>
+      </c>
       <c r="O35" t="s">
         <v>36</v>
       </c>
@@ -4956,6 +5061,9 @@
       <c r="M36" t="s">
         <v>35</v>
       </c>
+      <c r="N36" t="s">
+        <v>609</v>
+      </c>
       <c r="O36" t="s">
         <v>62</v>
       </c>
@@ -5027,6 +5135,9 @@
       <c r="M37" t="s">
         <v>35</v>
       </c>
+      <c r="N37" t="s">
+        <v>609</v>
+      </c>
       <c r="O37" t="s">
         <v>62</v>
       </c>
@@ -5098,6 +5209,9 @@
       <c r="M38" t="s">
         <v>35</v>
       </c>
+      <c r="N38" t="s">
+        <v>609</v>
+      </c>
       <c r="O38" t="s">
         <v>62</v>
       </c>
@@ -5169,6 +5283,9 @@
       <c r="M39" t="s">
         <v>35</v>
       </c>
+      <c r="N39" t="s">
+        <v>609</v>
+      </c>
       <c r="O39" t="s">
         <v>62</v>
       </c>
@@ -5240,6 +5357,9 @@
       <c r="M40" t="s">
         <v>35</v>
       </c>
+      <c r="N40" t="s">
+        <v>609</v>
+      </c>
       <c r="O40" t="s">
         <v>36</v>
       </c>
@@ -5314,6 +5434,9 @@
       <c r="M41" t="s">
         <v>35</v>
       </c>
+      <c r="N41" t="s">
+        <v>609</v>
+      </c>
       <c r="O41" t="s">
         <v>36</v>
       </c>
@@ -5388,6 +5511,9 @@
       <c r="M42" t="s">
         <v>35</v>
       </c>
+      <c r="N42" t="s">
+        <v>609</v>
+      </c>
       <c r="O42" t="s">
         <v>36</v>
       </c>
@@ -5459,6 +5585,9 @@
       <c r="M43" t="s">
         <v>35</v>
       </c>
+      <c r="N43" t="s">
+        <v>609</v>
+      </c>
       <c r="O43" t="s">
         <v>36</v>
       </c>
@@ -5533,6 +5662,9 @@
       <c r="M44" t="s">
         <v>35</v>
       </c>
+      <c r="N44" t="s">
+        <v>609</v>
+      </c>
       <c r="O44" t="s">
         <v>62</v>
       </c>
@@ -5604,6 +5736,9 @@
       <c r="M45" t="s">
         <v>35</v>
       </c>
+      <c r="N45" t="s">
+        <v>609</v>
+      </c>
       <c r="O45" t="s">
         <v>62</v>
       </c>
@@ -5675,6 +5810,9 @@
       <c r="M46" t="s">
         <v>35</v>
       </c>
+      <c r="N46" t="s">
+        <v>609</v>
+      </c>
       <c r="O46" t="s">
         <v>62</v>
       </c>
@@ -5746,6 +5884,9 @@
       <c r="M47" t="s">
         <v>35</v>
       </c>
+      <c r="N47" t="s">
+        <v>609</v>
+      </c>
       <c r="O47" t="s">
         <v>62</v>
       </c>
@@ -5817,6 +5958,9 @@
       <c r="M48" t="s">
         <v>35</v>
       </c>
+      <c r="N48" t="s">
+        <v>609</v>
+      </c>
       <c r="O48" t="s">
         <v>62</v>
       </c>
@@ -5888,6 +6032,9 @@
       <c r="M49" t="s">
         <v>35</v>
       </c>
+      <c r="N49" t="s">
+        <v>609</v>
+      </c>
       <c r="O49" t="s">
         <v>62</v>
       </c>
@@ -5959,6 +6106,9 @@
       <c r="M50" t="s">
         <v>85</v>
       </c>
+      <c r="N50" t="s">
+        <v>609</v>
+      </c>
       <c r="O50" t="s">
         <v>62</v>
       </c>
@@ -6030,6 +6180,9 @@
       <c r="M51" t="s">
         <v>46</v>
       </c>
+      <c r="N51" t="s">
+        <v>609</v>
+      </c>
       <c r="O51" t="s">
         <v>36</v>
       </c>
@@ -6101,6 +6254,9 @@
       <c r="M52" t="s">
         <v>35</v>
       </c>
+      <c r="N52" t="s">
+        <v>609</v>
+      </c>
       <c r="O52" t="s">
         <v>36</v>
       </c>
@@ -6172,6 +6328,9 @@
       <c r="M53" t="s">
         <v>35</v>
       </c>
+      <c r="N53" t="s">
+        <v>609</v>
+      </c>
       <c r="O53" t="s">
         <v>36</v>
       </c>
@@ -6243,6 +6402,9 @@
       <c r="M54" t="s">
         <v>35</v>
       </c>
+      <c r="N54" t="s">
+        <v>609</v>
+      </c>
       <c r="O54" t="s">
         <v>62</v>
       </c>
@@ -6314,6 +6476,9 @@
       <c r="M55" t="s">
         <v>35</v>
       </c>
+      <c r="N55" t="s">
+        <v>609</v>
+      </c>
       <c r="O55" t="s">
         <v>62</v>
       </c>
@@ -6385,6 +6550,9 @@
       <c r="M56" t="s">
         <v>35</v>
       </c>
+      <c r="N56" t="s">
+        <v>609</v>
+      </c>
       <c r="O56" t="s">
         <v>62</v>
       </c>
@@ -6456,6 +6624,9 @@
       <c r="M57" t="s">
         <v>35</v>
       </c>
+      <c r="N57" t="s">
+        <v>609</v>
+      </c>
       <c r="O57" t="s">
         <v>62</v>
       </c>
@@ -6527,6 +6698,9 @@
       <c r="M58" t="s">
         <v>35</v>
       </c>
+      <c r="N58" t="s">
+        <v>609</v>
+      </c>
       <c r="O58" t="s">
         <v>62</v>
       </c>
@@ -6598,6 +6772,9 @@
       <c r="M59" t="s">
         <v>35</v>
       </c>
+      <c r="N59" t="s">
+        <v>609</v>
+      </c>
       <c r="O59" t="s">
         <v>62</v>
       </c>
@@ -6669,6 +6846,9 @@
       <c r="M60" t="s">
         <v>35</v>
       </c>
+      <c r="N60" t="s">
+        <v>609</v>
+      </c>
       <c r="O60" t="s">
         <v>62</v>
       </c>
@@ -6740,6 +6920,9 @@
       <c r="M61" t="s">
         <v>35</v>
       </c>
+      <c r="N61" t="s">
+        <v>609</v>
+      </c>
       <c r="O61" t="s">
         <v>36</v>
       </c>
@@ -6811,6 +6994,9 @@
       <c r="M62" t="s">
         <v>35</v>
       </c>
+      <c r="N62" t="s">
+        <v>609</v>
+      </c>
       <c r="O62" t="s">
         <v>36</v>
       </c>
@@ -6882,6 +7068,9 @@
       <c r="M63" t="s">
         <v>35</v>
       </c>
+      <c r="N63" t="s">
+        <v>609</v>
+      </c>
       <c r="O63" t="s">
         <v>36</v>
       </c>
@@ -6956,6 +7145,9 @@
       <c r="M64" t="s">
         <v>35</v>
       </c>
+      <c r="N64" t="s">
+        <v>609</v>
+      </c>
       <c r="O64" t="s">
         <v>36</v>
       </c>
@@ -7030,6 +7222,9 @@
       <c r="M65" t="s">
         <v>35</v>
       </c>
+      <c r="N65" t="s">
+        <v>609</v>
+      </c>
       <c r="O65" t="s">
         <v>36</v>
       </c>
@@ -7104,6 +7299,9 @@
       <c r="M66" t="s">
         <v>35</v>
       </c>
+      <c r="N66" t="s">
+        <v>609</v>
+      </c>
       <c r="O66" t="s">
         <v>62</v>
       </c>
@@ -7175,6 +7373,9 @@
       <c r="M67" t="s">
         <v>35</v>
       </c>
+      <c r="N67" t="s">
+        <v>609</v>
+      </c>
       <c r="O67" t="s">
         <v>62</v>
       </c>
@@ -7246,6 +7447,9 @@
       <c r="M68" t="s">
         <v>46</v>
       </c>
+      <c r="N68" t="s">
+        <v>609</v>
+      </c>
       <c r="O68" t="s">
         <v>62</v>
       </c>
@@ -7317,6 +7521,9 @@
       <c r="M69" t="s">
         <v>46</v>
       </c>
+      <c r="N69" t="s">
+        <v>609</v>
+      </c>
       <c r="O69" t="s">
         <v>62</v>
       </c>
@@ -7388,6 +7595,9 @@
       <c r="M70" t="s">
         <v>46</v>
       </c>
+      <c r="N70" t="s">
+        <v>609</v>
+      </c>
       <c r="O70" t="s">
         <v>62</v>
       </c>
@@ -7459,6 +7669,9 @@
       <c r="M71" t="s">
         <v>35</v>
       </c>
+      <c r="N71" t="s">
+        <v>609</v>
+      </c>
       <c r="O71" t="s">
         <v>36</v>
       </c>
@@ -7533,6 +7746,9 @@
       <c r="M72" t="s">
         <v>35</v>
       </c>
+      <c r="N72" t="s">
+        <v>609</v>
+      </c>
       <c r="O72" t="s">
         <v>36</v>
       </c>
@@ -7607,6 +7823,9 @@
       <c r="M73" t="s">
         <v>35</v>
       </c>
+      <c r="N73" t="s">
+        <v>609</v>
+      </c>
       <c r="O73" t="s">
         <v>36</v>
       </c>
@@ -7681,6 +7900,9 @@
       <c r="M74" t="s">
         <v>35</v>
       </c>
+      <c r="N74" t="s">
+        <v>609</v>
+      </c>
       <c r="O74" t="s">
         <v>36</v>
       </c>
@@ -7755,6 +7977,9 @@
       <c r="M75" t="s">
         <v>35</v>
       </c>
+      <c r="N75" t="s">
+        <v>609</v>
+      </c>
       <c r="O75" t="s">
         <v>36</v>
       </c>
@@ -7829,6 +8054,9 @@
       <c r="M76" t="s">
         <v>35</v>
       </c>
+      <c r="N76" t="s">
+        <v>609</v>
+      </c>
       <c r="O76" t="s">
         <v>36</v>
       </c>
@@ -7903,6 +8131,9 @@
       <c r="M77" t="s">
         <v>35</v>
       </c>
+      <c r="N77" t="s">
+        <v>609</v>
+      </c>
       <c r="O77" t="s">
         <v>62</v>
       </c>
@@ -7974,6 +8205,9 @@
       <c r="M78" t="s">
         <v>35</v>
       </c>
+      <c r="N78" t="s">
+        <v>609</v>
+      </c>
       <c r="O78" t="s">
         <v>62</v>
       </c>
@@ -8045,6 +8279,9 @@
       <c r="M79" t="s">
         <v>85</v>
       </c>
+      <c r="N79" t="s">
+        <v>609</v>
+      </c>
       <c r="O79" t="s">
         <v>36</v>
       </c>
@@ -8116,6 +8353,9 @@
       <c r="M80" t="s">
         <v>85</v>
       </c>
+      <c r="N80" t="s">
+        <v>609</v>
+      </c>
       <c r="O80" t="s">
         <v>62</v>
       </c>
@@ -8187,6 +8427,9 @@
       <c r="M81" t="s">
         <v>46</v>
       </c>
+      <c r="N81" t="s">
+        <v>609</v>
+      </c>
       <c r="O81" t="s">
         <v>62</v>
       </c>
@@ -8258,6 +8501,9 @@
       <c r="M82" t="s">
         <v>46</v>
       </c>
+      <c r="N82" t="s">
+        <v>609</v>
+      </c>
       <c r="O82" t="s">
         <v>62</v>
       </c>
@@ -8329,6 +8575,9 @@
       <c r="M83" t="s">
         <v>46</v>
       </c>
+      <c r="N83" t="s">
+        <v>609</v>
+      </c>
       <c r="O83" t="s">
         <v>62</v>
       </c>
@@ -8400,6 +8649,9 @@
       <c r="M84" t="s">
         <v>35</v>
       </c>
+      <c r="N84" t="s">
+        <v>609</v>
+      </c>
       <c r="O84" t="s">
         <v>36</v>
       </c>
@@ -8471,6 +8723,9 @@
       <c r="M85" t="s">
         <v>35</v>
       </c>
+      <c r="N85" t="s">
+        <v>609</v>
+      </c>
       <c r="O85" t="s">
         <v>36</v>
       </c>
@@ -8542,6 +8797,9 @@
       <c r="M86" t="s">
         <v>35</v>
       </c>
+      <c r="N86" t="s">
+        <v>609</v>
+      </c>
       <c r="O86" t="s">
         <v>36</v>
       </c>
@@ -8616,6 +8874,9 @@
       <c r="M87" t="s">
         <v>35</v>
       </c>
+      <c r="N87" t="s">
+        <v>609</v>
+      </c>
       <c r="O87" t="s">
         <v>36</v>
       </c>
@@ -8690,6 +8951,9 @@
       <c r="M88" t="s">
         <v>85</v>
       </c>
+      <c r="N88" t="s">
+        <v>609</v>
+      </c>
       <c r="O88" t="s">
         <v>36</v>
       </c>
@@ -8761,6 +9025,9 @@
       <c r="M89" t="s">
         <v>35</v>
       </c>
+      <c r="N89" t="s">
+        <v>609</v>
+      </c>
       <c r="O89" t="s">
         <v>36</v>
       </c>
@@ -8835,6 +9102,9 @@
       <c r="M90" t="s">
         <v>35</v>
       </c>
+      <c r="N90" t="s">
+        <v>609</v>
+      </c>
       <c r="O90" t="s">
         <v>36</v>
       </c>
@@ -8909,6 +9179,9 @@
       <c r="M91" t="s">
         <v>35</v>
       </c>
+      <c r="N91" t="s">
+        <v>609</v>
+      </c>
       <c r="O91" t="s">
         <v>36</v>
       </c>
@@ -8980,6 +9253,9 @@
       <c r="M92" t="s">
         <v>35</v>
       </c>
+      <c r="N92" t="s">
+        <v>609</v>
+      </c>
       <c r="O92" t="s">
         <v>36</v>
       </c>
@@ -9054,6 +9330,9 @@
       <c r="M93" t="s">
         <v>35</v>
       </c>
+      <c r="N93" t="s">
+        <v>609</v>
+      </c>
       <c r="O93" t="s">
         <v>36</v>
       </c>
@@ -9128,6 +9407,9 @@
       <c r="M94" t="s">
         <v>35</v>
       </c>
+      <c r="N94" t="s">
+        <v>609</v>
+      </c>
       <c r="O94" t="s">
         <v>36</v>
       </c>
@@ -9202,6 +9484,9 @@
       <c r="M95" t="s">
         <v>35</v>
       </c>
+      <c r="N95" t="s">
+        <v>609</v>
+      </c>
       <c r="O95" t="s">
         <v>36</v>
       </c>
@@ -9276,6 +9561,9 @@
       <c r="M96" t="s">
         <v>85</v>
       </c>
+      <c r="N96" t="s">
+        <v>609</v>
+      </c>
       <c r="O96" t="s">
         <v>62</v>
       </c>
@@ -9347,6 +9635,9 @@
       <c r="M97" t="s">
         <v>35</v>
       </c>
+      <c r="N97" t="s">
+        <v>609</v>
+      </c>
       <c r="O97" t="s">
         <v>36</v>
       </c>
@@ -9421,6 +9712,9 @@
       <c r="M98" t="s">
         <v>35</v>
       </c>
+      <c r="N98" t="s">
+        <v>609</v>
+      </c>
       <c r="O98" t="s">
         <v>36</v>
       </c>
@@ -9495,6 +9789,9 @@
       <c r="M99" t="s">
         <v>35</v>
       </c>
+      <c r="N99" t="s">
+        <v>609</v>
+      </c>
       <c r="O99" t="s">
         <v>62</v>
       </c>
@@ -9569,6 +9866,9 @@
       <c r="M100" t="s">
         <v>35</v>
       </c>
+      <c r="N100" t="s">
+        <v>609</v>
+      </c>
       <c r="O100" t="s">
         <v>36</v>
       </c>
@@ -9643,6 +9943,9 @@
       <c r="M101" t="s">
         <v>35</v>
       </c>
+      <c r="N101" t="s">
+        <v>609</v>
+      </c>
       <c r="O101" t="s">
         <v>36</v>
       </c>
@@ -9717,6 +10020,9 @@
       <c r="M102" t="s">
         <v>85</v>
       </c>
+      <c r="N102" t="s">
+        <v>609</v>
+      </c>
       <c r="O102" t="s">
         <v>62</v>
       </c>
@@ -9788,6 +10094,9 @@
       <c r="M103" t="s">
         <v>35</v>
       </c>
+      <c r="N103" t="s">
+        <v>609</v>
+      </c>
       <c r="O103" t="s">
         <v>36</v>
       </c>
@@ -9862,6 +10171,9 @@
       <c r="M104" t="s">
         <v>85</v>
       </c>
+      <c r="N104" t="s">
+        <v>609</v>
+      </c>
       <c r="O104" t="s">
         <v>62</v>
       </c>
@@ -9933,6 +10245,9 @@
       <c r="M105" t="s">
         <v>35</v>
       </c>
+      <c r="N105" t="s">
+        <v>609</v>
+      </c>
       <c r="O105" t="s">
         <v>62</v>
       </c>
@@ -10007,6 +10322,9 @@
       <c r="M106" t="s">
         <v>46</v>
       </c>
+      <c r="N106" t="s">
+        <v>609</v>
+      </c>
       <c r="O106" t="s">
         <v>36</v>
       </c>
@@ -10078,6 +10396,9 @@
       <c r="M107" t="s">
         <v>46</v>
       </c>
+      <c r="N107" t="s">
+        <v>609</v>
+      </c>
       <c r="O107" t="s">
         <v>36</v>
       </c>
@@ -10149,6 +10470,9 @@
       <c r="M108" t="s">
         <v>46</v>
       </c>
+      <c r="N108" t="s">
+        <v>609</v>
+      </c>
       <c r="O108" t="s">
         <v>36</v>
       </c>
@@ -10220,6 +10544,9 @@
       <c r="M109" t="s">
         <v>85</v>
       </c>
+      <c r="N109" t="s">
+        <v>609</v>
+      </c>
       <c r="O109" t="s">
         <v>36</v>
       </c>
@@ -10291,6 +10618,9 @@
       <c r="M110" t="s">
         <v>85</v>
       </c>
+      <c r="N110" t="s">
+        <v>609</v>
+      </c>
       <c r="O110" t="s">
         <v>36</v>
       </c>
@@ -10362,6 +10692,9 @@
       <c r="M111" t="s">
         <v>46</v>
       </c>
+      <c r="N111" t="s">
+        <v>609</v>
+      </c>
       <c r="O111" t="s">
         <v>36</v>
       </c>
@@ -10433,6 +10766,9 @@
       <c r="M112" t="s">
         <v>85</v>
       </c>
+      <c r="N112" t="s">
+        <v>609</v>
+      </c>
       <c r="O112" t="s">
         <v>36</v>
       </c>
@@ -10504,6 +10840,9 @@
       <c r="M113" t="s">
         <v>35</v>
       </c>
+      <c r="N113" t="s">
+        <v>609</v>
+      </c>
       <c r="O113" t="s">
         <v>62</v>
       </c>
@@ -10575,6 +10914,9 @@
       <c r="M114" t="s">
         <v>35</v>
       </c>
+      <c r="N114" t="s">
+        <v>609</v>
+      </c>
       <c r="O114" t="s">
         <v>36</v>
       </c>
@@ -10649,6 +10991,9 @@
       <c r="M115" t="s">
         <v>85</v>
       </c>
+      <c r="N115" t="s">
+        <v>609</v>
+      </c>
       <c r="O115" t="s">
         <v>62</v>
       </c>
@@ -10720,6 +11065,9 @@
       <c r="M116" t="s">
         <v>85</v>
       </c>
+      <c r="N116" t="s">
+        <v>609</v>
+      </c>
       <c r="O116" t="s">
         <v>36</v>
       </c>
@@ -10791,6 +11139,9 @@
       <c r="M117" t="s">
         <v>35</v>
       </c>
+      <c r="N117" t="s">
+        <v>609</v>
+      </c>
       <c r="O117" t="s">
         <v>62</v>
       </c>
@@ -10862,6 +11213,9 @@
       <c r="M118" t="s">
         <v>35</v>
       </c>
+      <c r="N118" t="s">
+        <v>609</v>
+      </c>
       <c r="O118" t="s">
         <v>62</v>
       </c>
@@ -10933,6 +11287,9 @@
       <c r="M119" t="s">
         <v>35</v>
       </c>
+      <c r="N119" t="s">
+        <v>609</v>
+      </c>
       <c r="O119" t="s">
         <v>36</v>
       </c>
@@ -11007,6 +11364,9 @@
       <c r="M120" t="s">
         <v>85</v>
       </c>
+      <c r="N120" t="s">
+        <v>609</v>
+      </c>
       <c r="O120" t="s">
         <v>36</v>
       </c>
@@ -11075,6 +11435,9 @@
       <c r="M121" t="s">
         <v>85</v>
       </c>
+      <c r="N121" t="s">
+        <v>609</v>
+      </c>
       <c r="O121" t="s">
         <v>62</v>
       </c>
@@ -11143,6 +11506,9 @@
       <c r="M122" t="s">
         <v>85</v>
       </c>
+      <c r="N122" t="s">
+        <v>609</v>
+      </c>
       <c r="O122" t="s">
         <v>62</v>
       </c>
@@ -11214,6 +11580,9 @@
       <c r="M123" t="s">
         <v>85</v>
       </c>
+      <c r="N123" t="s">
+        <v>609</v>
+      </c>
       <c r="O123" t="s">
         <v>62</v>
       </c>
@@ -11282,6 +11651,9 @@
       <c r="M124" t="s">
         <v>85</v>
       </c>
+      <c r="N124" t="s">
+        <v>609</v>
+      </c>
       <c r="O124" t="s">
         <v>62</v>
       </c>
@@ -11350,6 +11722,9 @@
       <c r="M125" t="s">
         <v>35</v>
       </c>
+      <c r="N125" t="s">
+        <v>609</v>
+      </c>
       <c r="O125" t="s">
         <v>36</v>
       </c>
@@ -11424,6 +11799,9 @@
       <c r="M126" t="s">
         <v>35</v>
       </c>
+      <c r="N126" t="s">
+        <v>609</v>
+      </c>
       <c r="O126" t="s">
         <v>36</v>
       </c>
@@ -11498,6 +11876,9 @@
       <c r="M127" t="s">
         <v>35</v>
       </c>
+      <c r="N127" t="s">
+        <v>609</v>
+      </c>
       <c r="O127" t="s">
         <v>36</v>
       </c>
@@ -11572,6 +11953,9 @@
       <c r="M128" t="s">
         <v>85</v>
       </c>
+      <c r="N128" t="s">
+        <v>609</v>
+      </c>
       <c r="O128" t="s">
         <v>62</v>
       </c>
@@ -11643,6 +12027,9 @@
       <c r="M129" t="s">
         <v>35</v>
       </c>
+      <c r="N129" t="s">
+        <v>609</v>
+      </c>
       <c r="O129" t="s">
         <v>36</v>
       </c>
@@ -11717,6 +12104,9 @@
       <c r="M130" t="s">
         <v>35</v>
       </c>
+      <c r="N130" t="s">
+        <v>609</v>
+      </c>
       <c r="O130" t="s">
         <v>36</v>
       </c>
@@ -11791,6 +12181,9 @@
       <c r="M131" t="s">
         <v>35</v>
       </c>
+      <c r="N131" t="s">
+        <v>609</v>
+      </c>
       <c r="O131" t="s">
         <v>36</v>
       </c>
@@ -11865,6 +12258,9 @@
       <c r="M132" t="s">
         <v>35</v>
       </c>
+      <c r="N132" t="s">
+        <v>609</v>
+      </c>
       <c r="O132" t="s">
         <v>36</v>
       </c>
@@ -11939,6 +12335,9 @@
       <c r="M133" t="s">
         <v>35</v>
       </c>
+      <c r="N133" t="s">
+        <v>609</v>
+      </c>
       <c r="O133" t="s">
         <v>36</v>
       </c>
@@ -12013,6 +12412,9 @@
       <c r="M134" t="s">
         <v>35</v>
       </c>
+      <c r="N134" t="s">
+        <v>609</v>
+      </c>
       <c r="O134" t="s">
         <v>36</v>
       </c>
@@ -12087,6 +12489,9 @@
       <c r="M135" t="s">
         <v>35</v>
       </c>
+      <c r="N135" t="s">
+        <v>609</v>
+      </c>
       <c r="O135" t="s">
         <v>36</v>
       </c>
@@ -12161,6 +12566,9 @@
       <c r="M136" t="s">
         <v>35</v>
       </c>
+      <c r="N136" t="s">
+        <v>609</v>
+      </c>
       <c r="O136" t="s">
         <v>36</v>
       </c>
@@ -12235,6 +12643,9 @@
       <c r="M137" t="s">
         <v>35</v>
       </c>
+      <c r="N137" t="s">
+        <v>609</v>
+      </c>
       <c r="O137" t="s">
         <v>36</v>
       </c>
@@ -12309,6 +12720,9 @@
       <c r="M138" t="s">
         <v>35</v>
       </c>
+      <c r="N138" t="s">
+        <v>609</v>
+      </c>
       <c r="O138" t="s">
         <v>36</v>
       </c>
@@ -12383,6 +12797,9 @@
       <c r="M139" t="s">
         <v>35</v>
       </c>
+      <c r="N139" t="s">
+        <v>609</v>
+      </c>
       <c r="O139" t="s">
         <v>36</v>
       </c>
@@ -12457,6 +12874,9 @@
       <c r="M140" t="s">
         <v>35</v>
       </c>
+      <c r="N140" t="s">
+        <v>609</v>
+      </c>
       <c r="O140" t="s">
         <v>36</v>
       </c>
@@ -12531,6 +12951,9 @@
       <c r="M141" t="s">
         <v>35</v>
       </c>
+      <c r="N141" t="s">
+        <v>609</v>
+      </c>
       <c r="O141" t="s">
         <v>36</v>
       </c>
@@ -12605,6 +13028,9 @@
       <c r="M142" t="s">
         <v>46</v>
       </c>
+      <c r="N142" t="s">
+        <v>609</v>
+      </c>
       <c r="O142" t="s">
         <v>36</v>
       </c>
@@ -12676,6 +13102,9 @@
       <c r="M143" t="s">
         <v>46</v>
       </c>
+      <c r="N143" t="s">
+        <v>609</v>
+      </c>
       <c r="O143" t="s">
         <v>36</v>
       </c>
@@ -12747,6 +13176,9 @@
       <c r="M144" t="s">
         <v>85</v>
       </c>
+      <c r="N144" t="s">
+        <v>609</v>
+      </c>
       <c r="O144" t="s">
         <v>36</v>
       </c>
@@ -12818,6 +13250,9 @@
       <c r="M145" t="s">
         <v>85</v>
       </c>
+      <c r="N145" t="s">
+        <v>609</v>
+      </c>
       <c r="O145" t="s">
         <v>36</v>
       </c>
@@ -12889,6 +13324,9 @@
       <c r="M146" t="s">
         <v>85</v>
       </c>
+      <c r="N146" t="s">
+        <v>609</v>
+      </c>
       <c r="O146" t="s">
         <v>36</v>
       </c>
@@ -12960,6 +13398,9 @@
       <c r="M147" t="s">
         <v>85</v>
       </c>
+      <c r="N147" t="s">
+        <v>609</v>
+      </c>
       <c r="O147" t="s">
         <v>62</v>
       </c>
@@ -13031,6 +13472,9 @@
       <c r="M148" t="s">
         <v>35</v>
       </c>
+      <c r="N148" t="s">
+        <v>609</v>
+      </c>
       <c r="O148" t="s">
         <v>36</v>
       </c>
@@ -13105,6 +13549,9 @@
       <c r="M149" t="s">
         <v>35</v>
       </c>
+      <c r="N149" t="s">
+        <v>609</v>
+      </c>
       <c r="O149" t="s">
         <v>36</v>
       </c>
@@ -13179,6 +13626,9 @@
       <c r="M150" t="s">
         <v>35</v>
       </c>
+      <c r="N150" t="s">
+        <v>609</v>
+      </c>
       <c r="O150" t="s">
         <v>36</v>
       </c>
@@ -13253,6 +13703,9 @@
       <c r="M151" t="s">
         <v>35</v>
       </c>
+      <c r="N151" t="s">
+        <v>609</v>
+      </c>
       <c r="O151" t="s">
         <v>36</v>
       </c>
@@ -13327,6 +13780,9 @@
       <c r="M152" t="s">
         <v>85</v>
       </c>
+      <c r="N152" t="s">
+        <v>609</v>
+      </c>
       <c r="O152" t="s">
         <v>62</v>
       </c>
@@ -13398,6 +13854,9 @@
       <c r="M153" t="s">
         <v>35</v>
       </c>
+      <c r="N153" t="s">
+        <v>609</v>
+      </c>
       <c r="O153" t="s">
         <v>62</v>
       </c>
@@ -13469,6 +13928,9 @@
       <c r="M154" t="s">
         <v>85</v>
       </c>
+      <c r="N154" t="s">
+        <v>609</v>
+      </c>
       <c r="O154" t="s">
         <v>36</v>
       </c>
@@ -13540,6 +14002,9 @@
       <c r="M155" t="s">
         <v>85</v>
       </c>
+      <c r="N155" t="s">
+        <v>609</v>
+      </c>
       <c r="O155" t="s">
         <v>36</v>
       </c>
@@ -13611,6 +14076,9 @@
       <c r="M156" t="s">
         <v>85</v>
       </c>
+      <c r="N156" t="s">
+        <v>609</v>
+      </c>
       <c r="O156" t="s">
         <v>36</v>
       </c>
@@ -13682,6 +14150,9 @@
       <c r="M157" t="s">
         <v>85</v>
       </c>
+      <c r="N157" t="s">
+        <v>609</v>
+      </c>
       <c r="O157" t="s">
         <v>62</v>
       </c>
@@ -13753,6 +14224,9 @@
       <c r="M158" t="s">
         <v>85</v>
       </c>
+      <c r="N158" t="s">
+        <v>609</v>
+      </c>
       <c r="O158" t="s">
         <v>36</v>
       </c>
@@ -13824,6 +14298,9 @@
       <c r="M159" t="s">
         <v>85</v>
       </c>
+      <c r="N159" t="s">
+        <v>609</v>
+      </c>
       <c r="O159" t="s">
         <v>62</v>
       </c>
@@ -13895,6 +14372,9 @@
       <c r="M160" t="s">
         <v>85</v>
       </c>
+      <c r="N160" t="s">
+        <v>609</v>
+      </c>
       <c r="O160" t="s">
         <v>62</v>
       </c>
@@ -13966,6 +14446,9 @@
       <c r="M161" t="s">
         <v>85</v>
       </c>
+      <c r="N161" t="s">
+        <v>609</v>
+      </c>
       <c r="O161" t="s">
         <v>62</v>
       </c>
@@ -14037,6 +14520,9 @@
       <c r="M162" t="s">
         <v>85</v>
       </c>
+      <c r="N162" t="s">
+        <v>609</v>
+      </c>
       <c r="O162" t="s">
         <v>36</v>
       </c>
@@ -14108,6 +14594,9 @@
       <c r="M163" t="s">
         <v>85</v>
       </c>
+      <c r="N163" t="s">
+        <v>609</v>
+      </c>
       <c r="O163" t="s">
         <v>62</v>
       </c>
@@ -14179,6 +14668,9 @@
       <c r="M164" t="s">
         <v>85</v>
       </c>
+      <c r="N164" t="s">
+        <v>609</v>
+      </c>
       <c r="O164" t="s">
         <v>36</v>
       </c>
@@ -14250,6 +14742,9 @@
       <c r="M165" t="s">
         <v>46</v>
       </c>
+      <c r="N165" t="s">
+        <v>609</v>
+      </c>
       <c r="O165" t="s">
         <v>62</v>
       </c>
@@ -14321,6 +14816,9 @@
       <c r="M166" t="s">
         <v>85</v>
       </c>
+      <c r="N166" t="s">
+        <v>609</v>
+      </c>
       <c r="O166" t="s">
         <v>36</v>
       </c>
@@ -14392,6 +14890,9 @@
       <c r="M167" t="s">
         <v>85</v>
       </c>
+      <c r="N167" t="s">
+        <v>609</v>
+      </c>
       <c r="O167" t="s">
         <v>62</v>
       </c>
@@ -14463,6 +14964,9 @@
       <c r="M168" t="s">
         <v>85</v>
       </c>
+      <c r="N168" t="s">
+        <v>609</v>
+      </c>
       <c r="O168" t="s">
         <v>36</v>
       </c>
@@ -14534,6 +15038,9 @@
       <c r="M169" t="s">
         <v>85</v>
       </c>
+      <c r="N169" t="s">
+        <v>609</v>
+      </c>
       <c r="O169" t="s">
         <v>36</v>
       </c>
@@ -14605,6 +15112,9 @@
       <c r="M170" t="s">
         <v>85</v>
       </c>
+      <c r="N170" t="s">
+        <v>609</v>
+      </c>
       <c r="O170" t="s">
         <v>62</v>
       </c>
@@ -14676,6 +15186,9 @@
       <c r="M171" t="s">
         <v>85</v>
       </c>
+      <c r="N171" t="s">
+        <v>609</v>
+      </c>
       <c r="O171" t="s">
         <v>62</v>
       </c>
@@ -14747,6 +15260,9 @@
       <c r="M172" t="s">
         <v>85</v>
       </c>
+      <c r="N172" t="s">
+        <v>609</v>
+      </c>
       <c r="O172" t="s">
         <v>36</v>
       </c>
@@ -14818,6 +15334,9 @@
       <c r="M173" t="s">
         <v>85</v>
       </c>
+      <c r="N173" t="s">
+        <v>609</v>
+      </c>
       <c r="O173" t="s">
         <v>36</v>
       </c>
@@ -14889,6 +15408,9 @@
       <c r="M174" t="s">
         <v>85</v>
       </c>
+      <c r="N174" t="s">
+        <v>609</v>
+      </c>
       <c r="O174" t="s">
         <v>62</v>
       </c>
@@ -14960,6 +15482,9 @@
       <c r="M175" t="s">
         <v>85</v>
       </c>
+      <c r="N175" t="s">
+        <v>609</v>
+      </c>
       <c r="O175" t="s">
         <v>62</v>
       </c>
@@ -15031,6 +15556,9 @@
       <c r="M176" t="s">
         <v>85</v>
       </c>
+      <c r="N176" t="s">
+        <v>609</v>
+      </c>
       <c r="O176" t="s">
         <v>62</v>
       </c>
@@ -15102,6 +15630,9 @@
       <c r="M177" t="s">
         <v>85</v>
       </c>
+      <c r="N177" t="s">
+        <v>609</v>
+      </c>
       <c r="O177" t="s">
         <v>62</v>
       </c>
@@ -15173,6 +15704,9 @@
       <c r="M178" t="s">
         <v>85</v>
       </c>
+      <c r="N178" t="s">
+        <v>609</v>
+      </c>
       <c r="O178" t="s">
         <v>62</v>
       </c>
@@ -15244,6 +15778,9 @@
       <c r="M179" t="s">
         <v>85</v>
       </c>
+      <c r="N179" t="s">
+        <v>609</v>
+      </c>
       <c r="O179" t="s">
         <v>62</v>
       </c>
@@ -15315,6 +15852,9 @@
       <c r="M180" t="s">
         <v>85</v>
       </c>
+      <c r="N180" t="s">
+        <v>609</v>
+      </c>
       <c r="O180" t="s">
         <v>62</v>
       </c>
@@ -15386,6 +15926,9 @@
       <c r="M181" t="s">
         <v>85</v>
       </c>
+      <c r="N181" t="s">
+        <v>609</v>
+      </c>
       <c r="O181" t="s">
         <v>62</v>
       </c>
@@ -15457,6 +16000,9 @@
       <c r="M182" t="s">
         <v>85</v>
       </c>
+      <c r="N182" t="s">
+        <v>609</v>
+      </c>
       <c r="O182" t="s">
         <v>62</v>
       </c>
@@ -15528,6 +16074,9 @@
       <c r="M183" t="s">
         <v>85</v>
       </c>
+      <c r="N183" t="s">
+        <v>609</v>
+      </c>
       <c r="O183" t="s">
         <v>62</v>
       </c>
@@ -15599,6 +16148,9 @@
       <c r="M184" t="s">
         <v>85</v>
       </c>
+      <c r="N184" t="s">
+        <v>609</v>
+      </c>
       <c r="O184" t="s">
         <v>36</v>
       </c>
@@ -15670,6 +16222,9 @@
       <c r="M185" t="s">
         <v>85</v>
       </c>
+      <c r="N185" t="s">
+        <v>609</v>
+      </c>
       <c r="O185" t="s">
         <v>36</v>
       </c>
@@ -15741,6 +16296,9 @@
       <c r="M186" t="s">
         <v>85</v>
       </c>
+      <c r="N186" t="s">
+        <v>609</v>
+      </c>
       <c r="O186" t="s">
         <v>62</v>
       </c>
@@ -15812,6 +16370,9 @@
       <c r="M187" t="s">
         <v>85</v>
       </c>
+      <c r="N187" t="s">
+        <v>609</v>
+      </c>
       <c r="O187" t="s">
         <v>36</v>
       </c>
@@ -15883,6 +16444,9 @@
       <c r="M188" t="s">
         <v>85</v>
       </c>
+      <c r="N188" t="s">
+        <v>609</v>
+      </c>
       <c r="O188" t="s">
         <v>62</v>
       </c>
@@ -15954,6 +16518,9 @@
       <c r="M189" t="s">
         <v>85</v>
       </c>
+      <c r="N189" t="s">
+        <v>609</v>
+      </c>
       <c r="O189" t="s">
         <v>62</v>
       </c>
@@ -16025,6 +16592,9 @@
       <c r="M190" t="s">
         <v>85</v>
       </c>
+      <c r="N190" t="s">
+        <v>609</v>
+      </c>
       <c r="O190" t="s">
         <v>62</v>
       </c>
@@ -16096,6 +16666,9 @@
       <c r="M191" t="s">
         <v>85</v>
       </c>
+      <c r="N191" t="s">
+        <v>609</v>
+      </c>
       <c r="O191" t="s">
         <v>36</v>
       </c>
@@ -16167,6 +16740,9 @@
       <c r="M192" t="s">
         <v>85</v>
       </c>
+      <c r="N192" t="s">
+        <v>609</v>
+      </c>
       <c r="O192" t="s">
         <v>62</v>
       </c>
@@ -16238,6 +16814,9 @@
       <c r="M193" t="s">
         <v>85</v>
       </c>
+      <c r="N193" t="s">
+        <v>609</v>
+      </c>
       <c r="O193" t="s">
         <v>62</v>
       </c>
@@ -16309,6 +16888,9 @@
       <c r="M194" t="s">
         <v>85</v>
       </c>
+      <c r="N194" t="s">
+        <v>609</v>
+      </c>
       <c r="O194" t="s">
         <v>36</v>
       </c>
@@ -16380,6 +16962,9 @@
       <c r="M195" t="s">
         <v>85</v>
       </c>
+      <c r="N195" t="s">
+        <v>609</v>
+      </c>
       <c r="O195" t="s">
         <v>62</v>
       </c>
@@ -16451,6 +17036,9 @@
       <c r="M196" t="s">
         <v>85</v>
       </c>
+      <c r="N196" t="s">
+        <v>609</v>
+      </c>
       <c r="O196" t="s">
         <v>62</v>
       </c>
@@ -16522,6 +17110,9 @@
       <c r="M197" t="s">
         <v>85</v>
       </c>
+      <c r="N197" t="s">
+        <v>609</v>
+      </c>
       <c r="O197" t="s">
         <v>62</v>
       </c>
@@ -16593,6 +17184,9 @@
       <c r="M198" t="s">
         <v>85</v>
       </c>
+      <c r="N198" t="s">
+        <v>609</v>
+      </c>
       <c r="O198" t="s">
         <v>62</v>
       </c>
@@ -16664,6 +17258,9 @@
       <c r="M199" t="s">
         <v>85</v>
       </c>
+      <c r="N199" t="s">
+        <v>609</v>
+      </c>
       <c r="O199" t="s">
         <v>36</v>
       </c>
@@ -16735,6 +17332,9 @@
       <c r="M200" t="s">
         <v>85</v>
       </c>
+      <c r="N200" t="s">
+        <v>609</v>
+      </c>
       <c r="O200" t="s">
         <v>36</v>
       </c>
@@ -16806,6 +17406,9 @@
       <c r="M201" t="s">
         <v>85</v>
       </c>
+      <c r="N201" t="s">
+        <v>609</v>
+      </c>
       <c r="O201" t="s">
         <v>62</v>
       </c>
@@ -16877,6 +17480,9 @@
       <c r="M202" t="s">
         <v>85</v>
       </c>
+      <c r="N202" t="s">
+        <v>609</v>
+      </c>
       <c r="O202" t="s">
         <v>62</v>
       </c>
@@ -16948,6 +17554,9 @@
       <c r="M203" t="s">
         <v>85</v>
       </c>
+      <c r="N203" t="s">
+        <v>609</v>
+      </c>
       <c r="O203" t="s">
         <v>36</v>
       </c>
@@ -17019,6 +17628,9 @@
       <c r="M204" t="s">
         <v>85</v>
       </c>
+      <c r="N204" t="s">
+        <v>609</v>
+      </c>
       <c r="O204" t="s">
         <v>36</v>
       </c>
@@ -17090,6 +17702,9 @@
       <c r="M205" t="s">
         <v>85</v>
       </c>
+      <c r="N205" t="s">
+        <v>609</v>
+      </c>
       <c r="O205" t="s">
         <v>36</v>
       </c>
@@ -17161,6 +17776,9 @@
       <c r="M206" t="s">
         <v>85</v>
       </c>
+      <c r="N206" t="s">
+        <v>609</v>
+      </c>
       <c r="O206" t="s">
         <v>36</v>
       </c>
@@ -17232,6 +17850,9 @@
       <c r="M207" t="s">
         <v>85</v>
       </c>
+      <c r="N207" t="s">
+        <v>609</v>
+      </c>
       <c r="O207" t="s">
         <v>36</v>
       </c>
@@ -17303,6 +17924,9 @@
       <c r="M208" t="s">
         <v>85</v>
       </c>
+      <c r="N208" t="s">
+        <v>609</v>
+      </c>
       <c r="O208" t="s">
         <v>62</v>
       </c>
@@ -17374,6 +17998,9 @@
       <c r="M209" t="s">
         <v>85</v>
       </c>
+      <c r="N209" t="s">
+        <v>609</v>
+      </c>
       <c r="O209" t="s">
         <v>62</v>
       </c>
@@ -17445,6 +18072,9 @@
       <c r="M210" t="s">
         <v>85</v>
       </c>
+      <c r="N210" t="s">
+        <v>609</v>
+      </c>
       <c r="O210" t="s">
         <v>36</v>
       </c>
@@ -17516,6 +18146,9 @@
       <c r="M211" t="s">
         <v>85</v>
       </c>
+      <c r="N211" t="s">
+        <v>609</v>
+      </c>
       <c r="O211" t="s">
         <v>36</v>
       </c>
@@ -17587,6 +18220,9 @@
       <c r="M212" t="s">
         <v>85</v>
       </c>
+      <c r="N212" t="s">
+        <v>609</v>
+      </c>
       <c r="O212" t="s">
         <v>36</v>
       </c>
@@ -17658,6 +18294,9 @@
       <c r="M213" t="s">
         <v>85</v>
       </c>
+      <c r="N213" t="s">
+        <v>609</v>
+      </c>
       <c r="O213" t="s">
         <v>62</v>
       </c>
@@ -17729,6 +18368,9 @@
       <c r="M214" t="s">
         <v>85</v>
       </c>
+      <c r="N214" t="s">
+        <v>609</v>
+      </c>
       <c r="O214" t="s">
         <v>36</v>
       </c>
@@ -17800,6 +18442,9 @@
       <c r="M215" t="s">
         <v>85</v>
       </c>
+      <c r="N215" t="s">
+        <v>609</v>
+      </c>
       <c r="O215" t="s">
         <v>36</v>
       </c>
@@ -17871,6 +18516,9 @@
       <c r="M216" t="s">
         <v>85</v>
       </c>
+      <c r="N216" t="s">
+        <v>609</v>
+      </c>
       <c r="O216" t="s">
         <v>62</v>
       </c>
@@ -17942,6 +18590,9 @@
       <c r="M217" t="s">
         <v>85</v>
       </c>
+      <c r="N217" t="s">
+        <v>609</v>
+      </c>
       <c r="O217" t="s">
         <v>62</v>
       </c>
@@ -18013,6 +18664,9 @@
       <c r="M218" t="s">
         <v>85</v>
       </c>
+      <c r="N218" t="s">
+        <v>609</v>
+      </c>
       <c r="O218" t="s">
         <v>36</v>
       </c>
@@ -18084,6 +18738,9 @@
       <c r="M219" t="s">
         <v>85</v>
       </c>
+      <c r="N219" t="s">
+        <v>609</v>
+      </c>
       <c r="O219" t="s">
         <v>62</v>
       </c>
@@ -18155,6 +18812,9 @@
       <c r="M220" t="s">
         <v>85</v>
       </c>
+      <c r="N220" t="s">
+        <v>609</v>
+      </c>
       <c r="O220" t="s">
         <v>62</v>
       </c>
@@ -18226,6 +18886,9 @@
       <c r="M221" t="s">
         <v>85</v>
       </c>
+      <c r="N221" t="s">
+        <v>609</v>
+      </c>
       <c r="O221" t="s">
         <v>62</v>
       </c>
@@ -18297,6 +18960,9 @@
       <c r="M222" t="s">
         <v>85</v>
       </c>
+      <c r="N222" t="s">
+        <v>609</v>
+      </c>
       <c r="O222" t="s">
         <v>62</v>
       </c>
@@ -18368,6 +19034,9 @@
       <c r="M223" t="s">
         <v>85</v>
       </c>
+      <c r="N223" t="s">
+        <v>609</v>
+      </c>
       <c r="O223" t="s">
         <v>62</v>
       </c>
@@ -18439,6 +19108,9 @@
       <c r="M224" t="s">
         <v>85</v>
       </c>
+      <c r="N224" t="s">
+        <v>609</v>
+      </c>
       <c r="O224" t="s">
         <v>62</v>
       </c>
@@ -18510,6 +19182,9 @@
       <c r="M225" t="s">
         <v>85</v>
       </c>
+      <c r="N225" t="s">
+        <v>609</v>
+      </c>
       <c r="O225" t="s">
         <v>36</v>
       </c>
@@ -18581,6 +19256,9 @@
       <c r="M226" t="s">
         <v>85</v>
       </c>
+      <c r="N226" t="s">
+        <v>609</v>
+      </c>
       <c r="O226" t="s">
         <v>62</v>
       </c>
@@ -18652,6 +19330,9 @@
       <c r="M227" t="s">
         <v>85</v>
       </c>
+      <c r="N227" t="s">
+        <v>609</v>
+      </c>
       <c r="O227" t="s">
         <v>62</v>
       </c>
@@ -18723,6 +19404,9 @@
       <c r="M228" t="s">
         <v>85</v>
       </c>
+      <c r="N228" t="s">
+        <v>609</v>
+      </c>
       <c r="O228" t="s">
         <v>62</v>
       </c>
@@ -18794,6 +19478,9 @@
       <c r="M229" t="s">
         <v>85</v>
       </c>
+      <c r="N229" t="s">
+        <v>609</v>
+      </c>
       <c r="O229" t="s">
         <v>62</v>
       </c>
@@ -18865,6 +19552,9 @@
       <c r="M230" t="s">
         <v>85</v>
       </c>
+      <c r="N230" t="s">
+        <v>609</v>
+      </c>
       <c r="O230" t="s">
         <v>36</v>
       </c>
@@ -18936,6 +19626,9 @@
       <c r="M231" t="s">
         <v>85</v>
       </c>
+      <c r="N231" t="s">
+        <v>609</v>
+      </c>
       <c r="O231" t="s">
         <v>36</v>
       </c>
@@ -19007,6 +19700,9 @@
       <c r="M232" t="s">
         <v>85</v>
       </c>
+      <c r="N232" t="s">
+        <v>609</v>
+      </c>
       <c r="O232" t="s">
         <v>62</v>
       </c>
@@ -19078,6 +19774,9 @@
       <c r="M233" t="s">
         <v>85</v>
       </c>
+      <c r="N233" t="s">
+        <v>609</v>
+      </c>
       <c r="O233" t="s">
         <v>62</v>
       </c>
@@ -19149,6 +19848,9 @@
       <c r="M234" t="s">
         <v>85</v>
       </c>
+      <c r="N234" t="s">
+        <v>609</v>
+      </c>
       <c r="O234" t="s">
         <v>62</v>
       </c>
@@ -19220,6 +19922,9 @@
       <c r="M235" t="s">
         <v>85</v>
       </c>
+      <c r="N235" t="s">
+        <v>609</v>
+      </c>
       <c r="O235" t="s">
         <v>62</v>
       </c>
@@ -19291,6 +19996,9 @@
       <c r="M236" t="s">
         <v>85</v>
       </c>
+      <c r="N236" t="s">
+        <v>609</v>
+      </c>
       <c r="O236" t="s">
         <v>62</v>
       </c>
@@ -19362,6 +20070,9 @@
       <c r="M237" t="s">
         <v>85</v>
       </c>
+      <c r="N237" t="s">
+        <v>609</v>
+      </c>
       <c r="O237" t="s">
         <v>62</v>
       </c>
@@ -19433,6 +20144,9 @@
       <c r="M238" t="s">
         <v>85</v>
       </c>
+      <c r="N238" t="s">
+        <v>609</v>
+      </c>
       <c r="O238" t="s">
         <v>36</v>
       </c>
@@ -19504,6 +20218,9 @@
       <c r="M239" t="s">
         <v>85</v>
       </c>
+      <c r="N239" t="s">
+        <v>609</v>
+      </c>
       <c r="O239" t="s">
         <v>36</v>
       </c>
@@ -19575,6 +20292,9 @@
       <c r="M240" t="s">
         <v>85</v>
       </c>
+      <c r="N240" t="s">
+        <v>609</v>
+      </c>
       <c r="O240" t="s">
         <v>36</v>
       </c>
@@ -19646,6 +20366,9 @@
       <c r="M241" t="s">
         <v>85</v>
       </c>
+      <c r="N241" t="s">
+        <v>609</v>
+      </c>
       <c r="O241" t="s">
         <v>36</v>
       </c>
@@ -19717,6 +20440,9 @@
       <c r="M242" t="s">
         <v>35</v>
       </c>
+      <c r="N242" t="s">
+        <v>609</v>
+      </c>
       <c r="O242" t="s">
         <v>342</v>
       </c>
@@ -19788,6 +20514,9 @@
       <c r="M243" t="s">
         <v>35</v>
       </c>
+      <c r="N243" t="s">
+        <v>609</v>
+      </c>
       <c r="O243" t="s">
         <v>342</v>
       </c>
@@ -19859,6 +20588,9 @@
       <c r="M244" t="s">
         <v>35</v>
       </c>
+      <c r="N244" t="s">
+        <v>609</v>
+      </c>
       <c r="O244" t="s">
         <v>342</v>
       </c>
@@ -19930,6 +20662,9 @@
       <c r="M245" t="s">
         <v>35</v>
       </c>
+      <c r="N245" t="s">
+        <v>609</v>
+      </c>
       <c r="O245" t="s">
         <v>342</v>
       </c>
@@ -20001,6 +20736,9 @@
       <c r="M246" t="s">
         <v>35</v>
       </c>
+      <c r="N246" t="s">
+        <v>609</v>
+      </c>
       <c r="O246" t="s">
         <v>342</v>
       </c>
@@ -20072,6 +20810,9 @@
       <c r="M247" t="s">
         <v>35</v>
       </c>
+      <c r="N247" t="s">
+        <v>609</v>
+      </c>
       <c r="O247" t="s">
         <v>342</v>
       </c>
@@ -20143,6 +20884,9 @@
       <c r="M248" t="s">
         <v>35</v>
       </c>
+      <c r="N248" t="s">
+        <v>609</v>
+      </c>
       <c r="O248" t="s">
         <v>342</v>
       </c>
@@ -20214,6 +20958,9 @@
       <c r="M249" t="s">
         <v>35</v>
       </c>
+      <c r="N249" t="s">
+        <v>609</v>
+      </c>
       <c r="O249" t="s">
         <v>342</v>
       </c>
@@ -20285,6 +21032,9 @@
       <c r="M250" t="s">
         <v>35</v>
       </c>
+      <c r="N250" t="s">
+        <v>609</v>
+      </c>
       <c r="O250" t="s">
         <v>342</v>
       </c>
@@ -20356,6 +21106,9 @@
       <c r="M251" t="s">
         <v>35</v>
       </c>
+      <c r="N251" t="s">
+        <v>609</v>
+      </c>
       <c r="O251" t="s">
         <v>342</v>
       </c>
@@ -20427,6 +21180,9 @@
       <c r="M252" t="s">
         <v>85</v>
       </c>
+      <c r="N252" t="s">
+        <v>609</v>
+      </c>
       <c r="O252" t="s">
         <v>62</v>
       </c>
@@ -20498,6 +21254,9 @@
       <c r="M253" t="s">
         <v>85</v>
       </c>
+      <c r="N253" t="s">
+        <v>609</v>
+      </c>
       <c r="O253" t="s">
         <v>62</v>
       </c>
@@ -20569,6 +21328,9 @@
       <c r="M254" t="s">
         <v>46</v>
       </c>
+      <c r="N254" t="s">
+        <v>609</v>
+      </c>
       <c r="O254" t="s">
         <v>62</v>
       </c>
@@ -20640,6 +21402,9 @@
       <c r="M255" t="s">
         <v>35</v>
       </c>
+      <c r="N255" t="s">
+        <v>609</v>
+      </c>
       <c r="O255" t="s">
         <v>342</v>
       </c>
@@ -20711,6 +21476,9 @@
       <c r="M256" t="s">
         <v>35</v>
       </c>
+      <c r="N256" t="s">
+        <v>609</v>
+      </c>
       <c r="O256" t="s">
         <v>342</v>
       </c>
@@ -20782,6 +21550,9 @@
       <c r="M257" t="s">
         <v>35</v>
       </c>
+      <c r="N257" t="s">
+        <v>609</v>
+      </c>
       <c r="O257" t="s">
         <v>342</v>
       </c>
@@ -20853,6 +21624,9 @@
       <c r="M258" t="s">
         <v>35</v>
       </c>
+      <c r="N258" t="s">
+        <v>609</v>
+      </c>
       <c r="O258" t="s">
         <v>342</v>
       </c>
@@ -20924,6 +21698,9 @@
       <c r="M259" t="s">
         <v>35</v>
       </c>
+      <c r="N259" t="s">
+        <v>609</v>
+      </c>
       <c r="O259" t="s">
         <v>342</v>
       </c>
@@ -20995,6 +21772,9 @@
       <c r="M260" t="s">
         <v>35</v>
       </c>
+      <c r="N260" t="s">
+        <v>609</v>
+      </c>
       <c r="O260" t="s">
         <v>342</v>
       </c>
@@ -21066,6 +21846,9 @@
       <c r="M261" t="s">
         <v>35</v>
       </c>
+      <c r="N261" t="s">
+        <v>609</v>
+      </c>
       <c r="O261" t="s">
         <v>342</v>
       </c>
@@ -21137,6 +21920,9 @@
       <c r="M262" t="s">
         <v>35</v>
       </c>
+      <c r="N262" t="s">
+        <v>609</v>
+      </c>
       <c r="O262" t="s">
         <v>342</v>
       </c>
@@ -21208,6 +21994,9 @@
       <c r="M263" t="s">
         <v>35</v>
       </c>
+      <c r="N263" t="s">
+        <v>609</v>
+      </c>
       <c r="O263" t="s">
         <v>342</v>
       </c>
@@ -21279,6 +22068,9 @@
       <c r="M264" t="s">
         <v>35</v>
       </c>
+      <c r="N264" t="s">
+        <v>609</v>
+      </c>
       <c r="O264" t="s">
         <v>342</v>
       </c>
@@ -21350,6 +22142,9 @@
       <c r="M265" t="s">
         <v>35</v>
       </c>
+      <c r="N265" t="s">
+        <v>609</v>
+      </c>
       <c r="O265" t="s">
         <v>342</v>
       </c>
@@ -21421,6 +22216,9 @@
       <c r="M266" t="s">
         <v>35</v>
       </c>
+      <c r="N266" t="s">
+        <v>609</v>
+      </c>
       <c r="O266" t="s">
         <v>342</v>
       </c>
@@ -21492,6 +22290,9 @@
       <c r="M267" t="s">
         <v>35</v>
       </c>
+      <c r="N267" t="s">
+        <v>609</v>
+      </c>
       <c r="O267" t="s">
         <v>62</v>
       </c>
@@ -21566,6 +22367,9 @@
       <c r="M268" t="s">
         <v>35</v>
       </c>
+      <c r="N268" t="s">
+        <v>609</v>
+      </c>
       <c r="O268" t="s">
         <v>62</v>
       </c>
@@ -21637,6 +22441,9 @@
       <c r="M269" t="s">
         <v>35</v>
       </c>
+      <c r="N269" t="s">
+        <v>609</v>
+      </c>
       <c r="O269" t="s">
         <v>62</v>
       </c>
@@ -21711,6 +22518,9 @@
       <c r="M270" t="s">
         <v>35</v>
       </c>
+      <c r="N270" t="s">
+        <v>609</v>
+      </c>
       <c r="O270" t="s">
         <v>62</v>
       </c>
@@ -21785,6 +22595,9 @@
       <c r="M271" t="s">
         <v>35</v>
       </c>
+      <c r="N271" t="s">
+        <v>609</v>
+      </c>
       <c r="O271" t="s">
         <v>62</v>
       </c>
@@ -21859,6 +22672,9 @@
       <c r="M272" t="s">
         <v>35</v>
       </c>
+      <c r="N272" t="s">
+        <v>609</v>
+      </c>
       <c r="O272" t="s">
         <v>62</v>
       </c>
@@ -21933,6 +22749,9 @@
       <c r="M273" t="s">
         <v>35</v>
       </c>
+      <c r="N273" t="s">
+        <v>609</v>
+      </c>
       <c r="O273" t="s">
         <v>62</v>
       </c>
@@ -22007,6 +22826,9 @@
       <c r="M274" t="s">
         <v>35</v>
       </c>
+      <c r="N274" t="s">
+        <v>609</v>
+      </c>
       <c r="O274" t="s">
         <v>62</v>
       </c>
@@ -22081,6 +22903,9 @@
       <c r="M275" t="s">
         <v>35</v>
       </c>
+      <c r="N275" t="s">
+        <v>609</v>
+      </c>
       <c r="O275" t="s">
         <v>62</v>
       </c>
@@ -22155,6 +22980,9 @@
       <c r="M276" t="s">
         <v>35</v>
       </c>
+      <c r="N276" t="s">
+        <v>609</v>
+      </c>
       <c r="O276" t="s">
         <v>62</v>
       </c>
@@ -22229,6 +23057,9 @@
       <c r="M277" t="s">
         <v>35</v>
       </c>
+      <c r="N277" t="s">
+        <v>609</v>
+      </c>
       <c r="O277" t="s">
         <v>62</v>
       </c>
@@ -22303,6 +23134,9 @@
       <c r="M278" t="s">
         <v>35</v>
       </c>
+      <c r="N278" t="s">
+        <v>609</v>
+      </c>
       <c r="O278" t="s">
         <v>62</v>
       </c>
@@ -22377,6 +23211,9 @@
       <c r="M279" t="s">
         <v>35</v>
       </c>
+      <c r="N279" t="s">
+        <v>609</v>
+      </c>
       <c r="O279" t="s">
         <v>62</v>
       </c>
@@ -22451,6 +23288,9 @@
       <c r="M280" t="s">
         <v>35</v>
       </c>
+      <c r="N280" t="s">
+        <v>609</v>
+      </c>
       <c r="O280" t="s">
         <v>62</v>
       </c>
@@ -22522,6 +23362,9 @@
       <c r="M281" t="s">
         <v>35</v>
       </c>
+      <c r="N281" t="s">
+        <v>609</v>
+      </c>
       <c r="O281" t="s">
         <v>62</v>
       </c>
@@ -22593,6 +23436,9 @@
       <c r="M282" t="s">
         <v>35</v>
       </c>
+      <c r="N282" t="s">
+        <v>609</v>
+      </c>
       <c r="O282" t="s">
         <v>62</v>
       </c>
@@ -22664,6 +23510,9 @@
       <c r="M283" t="s">
         <v>35</v>
       </c>
+      <c r="N283" t="s">
+        <v>609</v>
+      </c>
       <c r="O283" t="s">
         <v>62</v>
       </c>
@@ -22735,6 +23584,9 @@
       <c r="M284" t="s">
         <v>35</v>
       </c>
+      <c r="N284" t="s">
+        <v>609</v>
+      </c>
       <c r="O284" t="s">
         <v>62</v>
       </c>
@@ -22809,6 +23661,9 @@
       <c r="M285" t="s">
         <v>35</v>
       </c>
+      <c r="N285" t="s">
+        <v>609</v>
+      </c>
       <c r="O285" t="s">
         <v>62</v>
       </c>
@@ -22880,6 +23735,9 @@
       <c r="M286" t="s">
         <v>35</v>
       </c>
+      <c r="N286" t="s">
+        <v>609</v>
+      </c>
       <c r="O286" t="s">
         <v>62</v>
       </c>
@@ -22954,6 +23812,9 @@
       <c r="M287" t="s">
         <v>35</v>
       </c>
+      <c r="N287" t="s">
+        <v>609</v>
+      </c>
       <c r="O287" t="s">
         <v>62</v>
       </c>
@@ -23028,6 +23889,9 @@
       <c r="M288" t="s">
         <v>35</v>
       </c>
+      <c r="N288" t="s">
+        <v>609</v>
+      </c>
       <c r="O288" t="s">
         <v>62</v>
       </c>
@@ -23102,6 +23966,9 @@
       <c r="M289" t="s">
         <v>35</v>
       </c>
+      <c r="N289" t="s">
+        <v>609</v>
+      </c>
       <c r="O289" t="s">
         <v>62</v>
       </c>
@@ -23176,6 +24043,9 @@
       <c r="M290" t="s">
         <v>35</v>
       </c>
+      <c r="N290" t="s">
+        <v>609</v>
+      </c>
       <c r="O290" t="s">
         <v>62</v>
       </c>
@@ -23250,6 +24120,9 @@
       <c r="M291" t="s">
         <v>46</v>
       </c>
+      <c r="N291" t="s">
+        <v>609</v>
+      </c>
       <c r="O291" t="s">
         <v>62</v>
       </c>
@@ -23321,6 +24194,9 @@
       <c r="M292" t="s">
         <v>46</v>
       </c>
+      <c r="N292" t="s">
+        <v>609</v>
+      </c>
       <c r="O292" t="s">
         <v>62</v>
       </c>
@@ -23392,6 +24268,9 @@
       <c r="M293" t="s">
         <v>35</v>
       </c>
+      <c r="N293" t="s">
+        <v>609</v>
+      </c>
       <c r="O293" t="s">
         <v>62</v>
       </c>
@@ -23466,6 +24345,9 @@
       <c r="M294" t="s">
         <v>46</v>
       </c>
+      <c r="N294" t="s">
+        <v>609</v>
+      </c>
       <c r="O294" t="s">
         <v>62</v>
       </c>
@@ -23537,6 +24419,9 @@
       <c r="M295" t="s">
         <v>46</v>
       </c>
+      <c r="N295" t="s">
+        <v>609</v>
+      </c>
       <c r="O295" t="s">
         <v>62</v>
       </c>
@@ -23608,6 +24493,9 @@
       <c r="M296" t="s">
         <v>46</v>
       </c>
+      <c r="N296" t="s">
+        <v>609</v>
+      </c>
       <c r="O296" t="s">
         <v>62</v>
       </c>
@@ -23679,6 +24567,9 @@
       <c r="M297" t="s">
         <v>46</v>
       </c>
+      <c r="N297" t="s">
+        <v>609</v>
+      </c>
       <c r="O297" t="s">
         <v>62</v>
       </c>
@@ -23750,6 +24641,9 @@
       <c r="M298" t="s">
         <v>35</v>
       </c>
+      <c r="N298" t="s">
+        <v>609</v>
+      </c>
       <c r="O298" t="s">
         <v>62</v>
       </c>
@@ -23824,6 +24718,9 @@
       <c r="M299" t="s">
         <v>35</v>
       </c>
+      <c r="N299" t="s">
+        <v>609</v>
+      </c>
       <c r="O299" t="s">
         <v>62</v>
       </c>
@@ -23898,6 +24795,9 @@
       <c r="M300" t="s">
         <v>85</v>
       </c>
+      <c r="N300" t="s">
+        <v>609</v>
+      </c>
       <c r="O300" t="s">
         <v>62</v>
       </c>
@@ -23969,6 +24869,9 @@
       <c r="M301" t="s">
         <v>85</v>
       </c>
+      <c r="N301" t="s">
+        <v>609</v>
+      </c>
       <c r="O301" t="s">
         <v>62</v>
       </c>
@@ -24040,6 +24943,9 @@
       <c r="M302" t="s">
         <v>85</v>
       </c>
+      <c r="N302" t="s">
+        <v>609</v>
+      </c>
       <c r="O302" t="s">
         <v>62</v>
       </c>
@@ -24111,6 +25017,9 @@
       <c r="M303" t="s">
         <v>85</v>
       </c>
+      <c r="N303" t="s">
+        <v>609</v>
+      </c>
       <c r="O303" t="s">
         <v>36</v>
       </c>
@@ -24182,6 +25091,9 @@
       <c r="M304" t="s">
         <v>85</v>
       </c>
+      <c r="N304" t="s">
+        <v>609</v>
+      </c>
       <c r="O304" t="s">
         <v>62</v>
       </c>
@@ -24253,6 +25165,9 @@
       <c r="M305" t="s">
         <v>85</v>
       </c>
+      <c r="N305" t="s">
+        <v>609</v>
+      </c>
       <c r="O305" t="s">
         <v>36</v>
       </c>
@@ -24324,6 +25239,9 @@
       <c r="M306" t="s">
         <v>85</v>
       </c>
+      <c r="N306" t="s">
+        <v>609</v>
+      </c>
       <c r="O306" t="s">
         <v>36</v>
       </c>
@@ -24395,6 +25313,9 @@
       <c r="M307" t="s">
         <v>85</v>
       </c>
+      <c r="N307" t="s">
+        <v>609</v>
+      </c>
       <c r="O307" t="s">
         <v>36</v>
       </c>
@@ -24466,6 +25387,9 @@
       <c r="M308" t="s">
         <v>85</v>
       </c>
+      <c r="N308" t="s">
+        <v>609</v>
+      </c>
       <c r="O308" t="s">
         <v>62</v>
       </c>
@@ -24537,6 +25461,9 @@
       <c r="M309" t="s">
         <v>85</v>
       </c>
+      <c r="N309" t="s">
+        <v>609</v>
+      </c>
       <c r="O309" t="s">
         <v>36</v>
       </c>
@@ -24608,6 +25535,9 @@
       <c r="M310" t="s">
         <v>85</v>
       </c>
+      <c r="N310" t="s">
+        <v>609</v>
+      </c>
       <c r="O310" t="s">
         <v>62</v>
       </c>
@@ -24679,6 +25609,9 @@
       <c r="M311" t="s">
         <v>85</v>
       </c>
+      <c r="N311" t="s">
+        <v>609</v>
+      </c>
       <c r="O311" t="s">
         <v>62</v>
       </c>
@@ -24750,6 +25683,9 @@
       <c r="M312" t="s">
         <v>35</v>
       </c>
+      <c r="N312" t="s">
+        <v>609</v>
+      </c>
       <c r="O312" t="s">
         <v>62</v>
       </c>
@@ -24821,6 +25757,9 @@
       <c r="M313" t="s">
         <v>35</v>
       </c>
+      <c r="N313" t="s">
+        <v>609</v>
+      </c>
       <c r="O313" t="s">
         <v>36</v>
       </c>
@@ -24895,6 +25834,9 @@
       <c r="M314" t="s">
         <v>35</v>
       </c>
+      <c r="N314" t="s">
+        <v>609</v>
+      </c>
       <c r="O314" t="s">
         <v>36</v>
       </c>
@@ -24969,6 +25911,9 @@
       <c r="M315" t="s">
         <v>35</v>
       </c>
+      <c r="N315" t="s">
+        <v>609</v>
+      </c>
       <c r="O315" t="s">
         <v>36</v>
       </c>
@@ -25043,6 +25988,9 @@
       <c r="M316" t="s">
         <v>85</v>
       </c>
+      <c r="N316" t="s">
+        <v>609</v>
+      </c>
       <c r="O316" t="s">
         <v>36</v>
       </c>
@@ -25114,6 +26062,9 @@
       <c r="M317" t="s">
         <v>35</v>
       </c>
+      <c r="N317" t="s">
+        <v>609</v>
+      </c>
       <c r="O317" t="s">
         <v>62</v>
       </c>
@@ -25188,6 +26139,9 @@
       <c r="M318" t="s">
         <v>35</v>
       </c>
+      <c r="N318" t="s">
+        <v>609</v>
+      </c>
       <c r="O318" t="s">
         <v>36</v>
       </c>
@@ -25262,6 +26216,9 @@
       <c r="M319" t="s">
         <v>35</v>
       </c>
+      <c r="N319" t="s">
+        <v>609</v>
+      </c>
       <c r="O319" t="s">
         <v>36</v>
       </c>
@@ -25336,6 +26293,9 @@
       <c r="M320" t="s">
         <v>46</v>
       </c>
+      <c r="N320" t="s">
+        <v>609</v>
+      </c>
       <c r="O320" t="s">
         <v>36</v>
       </c>
@@ -25407,6 +26367,9 @@
       <c r="M321" t="s">
         <v>35</v>
       </c>
+      <c r="N321" t="s">
+        <v>609</v>
+      </c>
       <c r="O321" t="s">
         <v>36</v>
       </c>
@@ -25481,6 +26444,9 @@
       <c r="M322" t="s">
         <v>35</v>
       </c>
+      <c r="N322" t="s">
+        <v>609</v>
+      </c>
       <c r="O322" t="s">
         <v>36</v>
       </c>
@@ -25555,6 +26521,9 @@
       <c r="M323" t="s">
         <v>46</v>
       </c>
+      <c r="N323" t="s">
+        <v>609</v>
+      </c>
       <c r="O323" t="s">
         <v>36</v>
       </c>
@@ -25626,6 +26595,9 @@
       <c r="M324" t="s">
         <v>35</v>
       </c>
+      <c r="N324" t="s">
+        <v>609</v>
+      </c>
       <c r="O324" t="s">
         <v>62</v>
       </c>
@@ -25700,6 +26672,9 @@
       <c r="M325" t="s">
         <v>35</v>
       </c>
+      <c r="N325" t="s">
+        <v>609</v>
+      </c>
       <c r="O325" t="s">
         <v>62</v>
       </c>
@@ -25771,6 +26746,9 @@
       <c r="M326" t="s">
         <v>35</v>
       </c>
+      <c r="N326" t="s">
+        <v>609</v>
+      </c>
       <c r="O326" t="s">
         <v>36</v>
       </c>
@@ -25845,6 +26823,9 @@
       <c r="M327" t="s">
         <v>35</v>
       </c>
+      <c r="N327" t="s">
+        <v>609</v>
+      </c>
       <c r="O327" t="s">
         <v>36</v>
       </c>
@@ -25919,6 +26900,9 @@
       <c r="M328" t="s">
         <v>35</v>
       </c>
+      <c r="N328" t="s">
+        <v>609</v>
+      </c>
       <c r="O328" t="s">
         <v>36</v>
       </c>
@@ -25993,6 +26977,9 @@
       <c r="M329" t="s">
         <v>35</v>
       </c>
+      <c r="N329" t="s">
+        <v>609</v>
+      </c>
       <c r="O329" t="s">
         <v>36</v>
       </c>
@@ -26067,6 +27054,9 @@
       <c r="M330" t="s">
         <v>35</v>
       </c>
+      <c r="N330" t="s">
+        <v>609</v>
+      </c>
       <c r="O330" t="s">
         <v>36</v>
       </c>
@@ -26141,6 +27131,9 @@
       <c r="M331" t="s">
         <v>35</v>
       </c>
+      <c r="N331" t="s">
+        <v>609</v>
+      </c>
       <c r="O331" t="s">
         <v>36</v>
       </c>
@@ -26215,6 +27208,9 @@
       <c r="M332" t="s">
         <v>35</v>
       </c>
+      <c r="N332" t="s">
+        <v>609</v>
+      </c>
       <c r="O332" t="s">
         <v>36</v>
       </c>
@@ -26289,6 +27285,9 @@
       <c r="M333" t="s">
         <v>35</v>
       </c>
+      <c r="N333" t="s">
+        <v>609</v>
+      </c>
       <c r="O333" t="s">
         <v>36</v>
       </c>
@@ -26363,6 +27362,9 @@
       <c r="M334" t="s">
         <v>35</v>
       </c>
+      <c r="N334" t="s">
+        <v>609</v>
+      </c>
       <c r="O334" t="s">
         <v>36</v>
       </c>
@@ -26437,6 +27439,9 @@
       <c r="M335" t="s">
         <v>35</v>
       </c>
+      <c r="N335" t="s">
+        <v>609</v>
+      </c>
       <c r="O335" t="s">
         <v>36</v>
       </c>
@@ -26511,6 +27516,9 @@
       <c r="M336" t="s">
         <v>35</v>
       </c>
+      <c r="N336" t="s">
+        <v>609</v>
+      </c>
       <c r="O336" t="s">
         <v>36</v>
       </c>
@@ -26585,6 +27593,9 @@
       <c r="M337" t="s">
         <v>35</v>
       </c>
+      <c r="N337" t="s">
+        <v>609</v>
+      </c>
       <c r="O337" t="s">
         <v>36</v>
       </c>
@@ -26659,6 +27670,9 @@
       <c r="M338" t="s">
         <v>35</v>
       </c>
+      <c r="N338" t="s">
+        <v>609</v>
+      </c>
       <c r="O338" t="s">
         <v>36</v>
       </c>
@@ -26733,6 +27747,9 @@
       <c r="M339" t="s">
         <v>35</v>
       </c>
+      <c r="N339" t="s">
+        <v>609</v>
+      </c>
       <c r="O339" t="s">
         <v>36</v>
       </c>
@@ -26807,6 +27824,9 @@
       <c r="M340" t="s">
         <v>35</v>
       </c>
+      <c r="N340" t="s">
+        <v>609</v>
+      </c>
       <c r="O340" t="s">
         <v>36</v>
       </c>
@@ -26881,6 +27901,9 @@
       <c r="M341" t="s">
         <v>35</v>
       </c>
+      <c r="N341" t="s">
+        <v>609</v>
+      </c>
       <c r="O341" t="s">
         <v>36</v>
       </c>
@@ -26955,6 +27978,9 @@
       <c r="M342" t="s">
         <v>35</v>
       </c>
+      <c r="N342" t="s">
+        <v>609</v>
+      </c>
       <c r="O342" t="s">
         <v>36</v>
       </c>
@@ -27029,6 +28055,9 @@
       <c r="M343" t="s">
         <v>35</v>
       </c>
+      <c r="N343" t="s">
+        <v>609</v>
+      </c>
       <c r="O343" t="s">
         <v>36</v>
       </c>
@@ -27103,6 +28132,9 @@
       <c r="M344" t="s">
         <v>35</v>
       </c>
+      <c r="N344" t="s">
+        <v>609</v>
+      </c>
       <c r="O344" t="s">
         <v>36</v>
       </c>
@@ -27177,6 +28209,9 @@
       <c r="M345" t="s">
         <v>35</v>
       </c>
+      <c r="N345" t="s">
+        <v>609</v>
+      </c>
       <c r="O345" t="s">
         <v>36</v>
       </c>
@@ -27251,6 +28286,9 @@
       <c r="M346" t="s">
         <v>35</v>
       </c>
+      <c r="N346" t="s">
+        <v>609</v>
+      </c>
       <c r="O346" t="s">
         <v>36</v>
       </c>
@@ -27325,6 +28363,9 @@
       <c r="M347" t="s">
         <v>35</v>
       </c>
+      <c r="N347" t="s">
+        <v>609</v>
+      </c>
       <c r="O347" t="s">
         <v>36</v>
       </c>
@@ -27399,6 +28440,9 @@
       <c r="M348" t="s">
         <v>35</v>
       </c>
+      <c r="N348" t="s">
+        <v>609</v>
+      </c>
       <c r="O348" t="s">
         <v>36</v>
       </c>
@@ -27473,6 +28517,9 @@
       <c r="M349" t="s">
         <v>35</v>
       </c>
+      <c r="N349" t="s">
+        <v>609</v>
+      </c>
       <c r="O349" t="s">
         <v>36</v>
       </c>
@@ -27547,6 +28594,9 @@
       <c r="M350" t="s">
         <v>35</v>
       </c>
+      <c r="N350" t="s">
+        <v>609</v>
+      </c>
       <c r="O350" t="s">
         <v>36</v>
       </c>
@@ -27621,6 +28671,9 @@
       <c r="M351" t="s">
         <v>85</v>
       </c>
+      <c r="N351" t="s">
+        <v>609</v>
+      </c>
       <c r="O351" t="s">
         <v>62</v>
       </c>
@@ -27692,6 +28745,9 @@
       <c r="M352" t="s">
         <v>35</v>
       </c>
+      <c r="N352" t="s">
+        <v>609</v>
+      </c>
       <c r="O352" t="s">
         <v>62</v>
       </c>
@@ -27766,6 +28822,9 @@
       <c r="M353" t="s">
         <v>35</v>
       </c>
+      <c r="N353" t="s">
+        <v>609</v>
+      </c>
       <c r="O353" t="s">
         <v>36</v>
       </c>
@@ -27837,6 +28896,9 @@
       <c r="M354" t="s">
         <v>85</v>
       </c>
+      <c r="N354" t="s">
+        <v>609</v>
+      </c>
       <c r="O354" t="s">
         <v>36</v>
       </c>
@@ -27908,6 +28970,9 @@
       <c r="M355" t="s">
         <v>85</v>
       </c>
+      <c r="N355" t="s">
+        <v>609</v>
+      </c>
       <c r="O355" t="s">
         <v>62</v>
       </c>
@@ -27979,6 +29044,9 @@
       <c r="M356" t="s">
         <v>85</v>
       </c>
+      <c r="N356" t="s">
+        <v>609</v>
+      </c>
       <c r="O356" t="s">
         <v>62</v>
       </c>
@@ -28047,6 +29115,9 @@
       <c r="M357" t="s">
         <v>35</v>
       </c>
+      <c r="N357" t="s">
+        <v>609</v>
+      </c>
       <c r="O357" t="s">
         <v>36</v>
       </c>
@@ -28118,6 +29189,9 @@
       <c r="M358" t="s">
         <v>85</v>
       </c>
+      <c r="N358" t="s">
+        <v>609</v>
+      </c>
       <c r="O358" t="s">
         <v>62</v>
       </c>
@@ -28186,6 +29260,9 @@
       <c r="M359" t="s">
         <v>85</v>
       </c>
+      <c r="N359" t="s">
+        <v>609</v>
+      </c>
       <c r="O359" t="s">
         <v>62</v>
       </c>
@@ -28254,6 +29331,9 @@
       <c r="M360" t="s">
         <v>35</v>
       </c>
+      <c r="N360" t="s">
+        <v>609</v>
+      </c>
       <c r="O360" t="s">
         <v>62</v>
       </c>
@@ -28325,6 +29405,9 @@
       <c r="M361" t="s">
         <v>35</v>
       </c>
+      <c r="N361" t="s">
+        <v>609</v>
+      </c>
       <c r="O361" t="s">
         <v>62</v>
       </c>
@@ -28396,6 +29479,9 @@
       <c r="M362" t="s">
         <v>85</v>
       </c>
+      <c r="N362" t="s">
+        <v>609</v>
+      </c>
       <c r="O362" t="s">
         <v>62</v>
       </c>
@@ -28467,6 +29553,9 @@
       <c r="M363" t="s">
         <v>85</v>
       </c>
+      <c r="N363" t="s">
+        <v>609</v>
+      </c>
       <c r="O363" t="s">
         <v>62</v>
       </c>
@@ -28538,6 +29627,9 @@
       <c r="M364" t="s">
         <v>46</v>
       </c>
+      <c r="N364" t="s">
+        <v>609</v>
+      </c>
       <c r="O364" t="s">
         <v>62</v>
       </c>
@@ -28609,6 +29701,9 @@
       <c r="M365" t="s">
         <v>35</v>
       </c>
+      <c r="N365" t="s">
+        <v>609</v>
+      </c>
       <c r="O365" t="s">
         <v>62</v>
       </c>
@@ -28680,6 +29775,9 @@
       <c r="M366" t="s">
         <v>35</v>
       </c>
+      <c r="N366" t="s">
+        <v>609</v>
+      </c>
       <c r="O366" t="s">
         <v>62</v>
       </c>
@@ -28751,6 +29849,9 @@
       <c r="M367" t="s">
         <v>85</v>
       </c>
+      <c r="N367" t="s">
+        <v>609</v>
+      </c>
       <c r="O367" t="s">
         <v>62</v>
       </c>
@@ -28822,6 +29923,9 @@
       <c r="M368" t="s">
         <v>85</v>
       </c>
+      <c r="N368" t="s">
+        <v>609</v>
+      </c>
       <c r="O368" t="s">
         <v>36</v>
       </c>
@@ -28893,6 +29997,9 @@
       <c r="M369" t="s">
         <v>35</v>
       </c>
+      <c r="N369" t="s">
+        <v>609</v>
+      </c>
       <c r="O369" t="s">
         <v>62</v>
       </c>
@@ -28964,6 +30071,9 @@
       <c r="M370" t="s">
         <v>85</v>
       </c>
+      <c r="N370" t="s">
+        <v>609</v>
+      </c>
       <c r="O370" t="s">
         <v>36</v>
       </c>
@@ -29035,6 +30145,9 @@
       <c r="M371" t="s">
         <v>85</v>
       </c>
+      <c r="N371" t="s">
+        <v>609</v>
+      </c>
       <c r="O371" t="s">
         <v>36</v>
       </c>
@@ -29106,6 +30219,9 @@
       <c r="M372" t="s">
         <v>46</v>
       </c>
+      <c r="N372" t="s">
+        <v>609</v>
+      </c>
       <c r="O372" t="s">
         <v>62</v>
       </c>
@@ -29177,6 +30293,9 @@
       <c r="M373" t="s">
         <v>85</v>
       </c>
+      <c r="N373" t="s">
+        <v>609</v>
+      </c>
       <c r="O373" t="s">
         <v>36</v>
       </c>
@@ -29245,6 +30364,9 @@
       <c r="M374" t="s">
         <v>85</v>
       </c>
+      <c r="N374" t="s">
+        <v>609</v>
+      </c>
       <c r="O374" t="s">
         <v>36</v>
       </c>
@@ -29313,6 +30435,9 @@
       <c r="M375" t="s">
         <v>85</v>
       </c>
+      <c r="N375" t="s">
+        <v>609</v>
+      </c>
       <c r="O375" t="s">
         <v>62</v>
       </c>
@@ -29381,6 +30506,9 @@
       <c r="M376" t="s">
         <v>85</v>
       </c>
+      <c r="N376" t="s">
+        <v>609</v>
+      </c>
       <c r="O376" t="s">
         <v>62</v>
       </c>
@@ -29452,6 +30580,9 @@
       <c r="M377" t="s">
         <v>85</v>
       </c>
+      <c r="N377" t="s">
+        <v>609</v>
+      </c>
       <c r="O377" t="s">
         <v>36</v>
       </c>
@@ -29523,6 +30654,9 @@
       <c r="M378" t="s">
         <v>85</v>
       </c>
+      <c r="N378" t="s">
+        <v>609</v>
+      </c>
       <c r="O378" t="s">
         <v>62</v>
       </c>
@@ -29594,6 +30728,9 @@
       <c r="M379" t="s">
         <v>85</v>
       </c>
+      <c r="N379" t="s">
+        <v>609</v>
+      </c>
       <c r="O379" t="s">
         <v>36</v>
       </c>
@@ -29665,6 +30802,9 @@
       <c r="M380" t="s">
         <v>85</v>
       </c>
+      <c r="N380" t="s">
+        <v>609</v>
+      </c>
       <c r="O380" t="s">
         <v>36</v>
       </c>
@@ -29736,6 +30876,9 @@
       <c r="M381" t="s">
         <v>35</v>
       </c>
+      <c r="N381" t="s">
+        <v>609</v>
+      </c>
       <c r="O381" t="s">
         <v>62</v>
       </c>
@@ -29807,6 +30950,9 @@
       <c r="M382" t="s">
         <v>85</v>
       </c>
+      <c r="N382" t="s">
+        <v>609</v>
+      </c>
       <c r="O382" t="s">
         <v>62</v>
       </c>
@@ -29878,6 +31024,9 @@
       <c r="M383" t="s">
         <v>85</v>
       </c>
+      <c r="N383" t="s">
+        <v>609</v>
+      </c>
       <c r="O383" t="s">
         <v>62</v>
       </c>
@@ -29949,6 +31098,9 @@
       <c r="M384" t="s">
         <v>85</v>
       </c>
+      <c r="N384" t="s">
+        <v>609</v>
+      </c>
       <c r="O384" t="s">
         <v>62</v>
       </c>
@@ -30020,6 +31172,9 @@
       <c r="M385" t="s">
         <v>35</v>
       </c>
+      <c r="N385" t="s">
+        <v>609</v>
+      </c>
       <c r="O385" t="s">
         <v>36</v>
       </c>
@@ -30094,6 +31249,9 @@
       <c r="M386" t="s">
         <v>85</v>
       </c>
+      <c r="N386" t="s">
+        <v>609</v>
+      </c>
       <c r="O386" t="s">
         <v>62</v>
       </c>
@@ -30165,6 +31323,9 @@
       <c r="M387" t="s">
         <v>85</v>
       </c>
+      <c r="N387" t="s">
+        <v>609</v>
+      </c>
       <c r="O387" t="s">
         <v>62</v>
       </c>
@@ -30236,6 +31397,9 @@
       <c r="M388" t="s">
         <v>85</v>
       </c>
+      <c r="N388" t="s">
+        <v>609</v>
+      </c>
       <c r="O388" t="s">
         <v>36</v>
       </c>
@@ -30307,6 +31471,9 @@
       <c r="M389" t="s">
         <v>85</v>
       </c>
+      <c r="N389" t="s">
+        <v>609</v>
+      </c>
       <c r="O389" t="s">
         <v>62</v>
       </c>
@@ -30378,6 +31545,9 @@
       <c r="M390" t="s">
         <v>35</v>
       </c>
+      <c r="N390" t="s">
+        <v>609</v>
+      </c>
       <c r="O390" t="s">
         <v>36</v>
       </c>
@@ -30449,6 +31619,9 @@
       <c r="M391" t="s">
         <v>35</v>
       </c>
+      <c r="N391" t="s">
+        <v>609</v>
+      </c>
       <c r="O391" t="s">
         <v>36</v>
       </c>
@@ -30523,6 +31696,9 @@
       <c r="M392" t="s">
         <v>35</v>
       </c>
+      <c r="N392" t="s">
+        <v>609</v>
+      </c>
       <c r="O392" t="s">
         <v>62</v>
       </c>
@@ -30597,6 +31773,9 @@
       <c r="M393" t="s">
         <v>85</v>
       </c>
+      <c r="N393" t="s">
+        <v>609</v>
+      </c>
       <c r="O393" t="s">
         <v>62</v>
       </c>
@@ -30665,6 +31844,9 @@
       <c r="M394" t="s">
         <v>46</v>
       </c>
+      <c r="N394" t="s">
+        <v>609</v>
+      </c>
       <c r="O394" t="s">
         <v>62</v>
       </c>
@@ -30736,6 +31918,9 @@
       <c r="M395" t="s">
         <v>46</v>
       </c>
+      <c r="N395" t="s">
+        <v>609</v>
+      </c>
       <c r="O395" t="s">
         <v>62</v>
       </c>
@@ -30807,6 +31992,9 @@
       <c r="M396" t="s">
         <v>46</v>
       </c>
+      <c r="N396" t="s">
+        <v>609</v>
+      </c>
       <c r="O396" t="s">
         <v>62</v>
       </c>
@@ -30878,6 +32066,9 @@
       <c r="M397" t="s">
         <v>85</v>
       </c>
+      <c r="N397" t="s">
+        <v>609</v>
+      </c>
       <c r="O397" t="s">
         <v>62</v>
       </c>
@@ -30949,6 +32140,9 @@
       <c r="M398" t="s">
         <v>85</v>
       </c>
+      <c r="N398" t="s">
+        <v>609</v>
+      </c>
       <c r="O398" t="s">
         <v>62</v>
       </c>
@@ -31020,6 +32214,9 @@
       <c r="M399" t="s">
         <v>85</v>
       </c>
+      <c r="N399" t="s">
+        <v>609</v>
+      </c>
       <c r="O399" t="s">
         <v>36</v>
       </c>
@@ -31091,6 +32288,9 @@
       <c r="M400" t="s">
         <v>46</v>
       </c>
+      <c r="N400" t="s">
+        <v>609</v>
+      </c>
       <c r="O400" t="s">
         <v>36</v>
       </c>
@@ -31162,6 +32362,9 @@
       <c r="M401" t="s">
         <v>85</v>
       </c>
+      <c r="N401" t="s">
+        <v>609</v>
+      </c>
       <c r="O401" t="s">
         <v>62</v>
       </c>
@@ -31233,6 +32436,9 @@
       <c r="M402" t="s">
         <v>85</v>
       </c>
+      <c r="N402" t="s">
+        <v>609</v>
+      </c>
       <c r="O402" t="s">
         <v>36</v>
       </c>
@@ -31301,6 +32507,9 @@
       <c r="M403" t="s">
         <v>85</v>
       </c>
+      <c r="N403" t="s">
+        <v>609</v>
+      </c>
       <c r="O403" t="s">
         <v>62</v>
       </c>
@@ -31372,6 +32581,9 @@
       <c r="M404" t="s">
         <v>46</v>
       </c>
+      <c r="N404" t="s">
+        <v>609</v>
+      </c>
       <c r="O404" t="s">
         <v>36</v>
       </c>
@@ -31443,6 +32655,9 @@
       <c r="M405" t="s">
         <v>35</v>
       </c>
+      <c r="N405" t="s">
+        <v>609</v>
+      </c>
       <c r="O405" t="s">
         <v>36</v>
       </c>
@@ -31517,6 +32732,9 @@
       <c r="M406" t="s">
         <v>35</v>
       </c>
+      <c r="N406" t="s">
+        <v>609</v>
+      </c>
       <c r="O406" t="s">
         <v>36</v>
       </c>
@@ -31591,6 +32809,9 @@
       <c r="M407" t="s">
         <v>46</v>
       </c>
+      <c r="N407" t="s">
+        <v>609</v>
+      </c>
       <c r="O407" t="s">
         <v>36</v>
       </c>
@@ -31662,6 +32883,9 @@
       <c r="M408" t="s">
         <v>85</v>
       </c>
+      <c r="N408" t="s">
+        <v>609</v>
+      </c>
       <c r="O408" t="s">
         <v>62</v>
       </c>
@@ -31733,6 +32957,9 @@
       <c r="M409" t="s">
         <v>46</v>
       </c>
+      <c r="N409" t="s">
+        <v>609</v>
+      </c>
       <c r="O409" t="s">
         <v>36</v>
       </c>
@@ -31804,6 +33031,9 @@
       <c r="M410" t="s">
         <v>85</v>
       </c>
+      <c r="N410" t="s">
+        <v>609</v>
+      </c>
       <c r="O410" t="s">
         <v>36</v>
       </c>
@@ -31875,6 +33105,9 @@
       <c r="M411" t="s">
         <v>35</v>
       </c>
+      <c r="N411" t="s">
+        <v>609</v>
+      </c>
       <c r="O411" t="s">
         <v>36</v>
       </c>
@@ -31949,6 +33182,9 @@
       <c r="M412" t="s">
         <v>46</v>
       </c>
+      <c r="N412" t="s">
+        <v>609</v>
+      </c>
       <c r="O412" t="s">
         <v>36</v>
       </c>
@@ -32020,6 +33256,9 @@
       <c r="M413" t="s">
         <v>46</v>
       </c>
+      <c r="N413" t="s">
+        <v>609</v>
+      </c>
       <c r="O413" t="s">
         <v>36</v>
       </c>
@@ -32091,6 +33330,9 @@
       <c r="M414" t="s">
         <v>46</v>
       </c>
+      <c r="N414" t="s">
+        <v>609</v>
+      </c>
       <c r="O414" t="s">
         <v>36</v>
       </c>
@@ -32162,6 +33404,9 @@
       <c r="M415" t="s">
         <v>46</v>
       </c>
+      <c r="N415" t="s">
+        <v>609</v>
+      </c>
       <c r="O415" t="s">
         <v>36</v>
       </c>
@@ -32233,6 +33478,9 @@
       <c r="M416" t="s">
         <v>46</v>
       </c>
+      <c r="N416" t="s">
+        <v>609</v>
+      </c>
       <c r="O416" t="s">
         <v>36</v>
       </c>
@@ -32304,6 +33552,9 @@
       <c r="M417" t="s">
         <v>35</v>
       </c>
+      <c r="N417" t="s">
+        <v>609</v>
+      </c>
       <c r="O417" t="s">
         <v>36</v>
       </c>
@@ -32375,6 +33626,9 @@
       <c r="M418" t="s">
         <v>35</v>
       </c>
+      <c r="N418" t="s">
+        <v>609</v>
+      </c>
       <c r="O418" t="s">
         <v>36</v>
       </c>
@@ -32446,6 +33700,9 @@
       <c r="M419" t="s">
         <v>35</v>
       </c>
+      <c r="N419" t="s">
+        <v>609</v>
+      </c>
       <c r="O419" t="s">
         <v>36</v>
       </c>
@@ -32517,6 +33774,9 @@
       <c r="M420" t="s">
         <v>35</v>
       </c>
+      <c r="N420" t="s">
+        <v>609</v>
+      </c>
       <c r="O420" t="s">
         <v>36</v>
       </c>
@@ -32591,6 +33851,9 @@
       <c r="M421" t="s">
         <v>35</v>
       </c>
+      <c r="N421" t="s">
+        <v>609</v>
+      </c>
       <c r="O421" t="s">
         <v>36</v>
       </c>
@@ -32665,6 +33928,9 @@
       <c r="M422" t="s">
         <v>35</v>
       </c>
+      <c r="N422" t="s">
+        <v>609</v>
+      </c>
       <c r="O422" t="s">
         <v>36</v>
       </c>
@@ -32739,6 +34005,9 @@
       <c r="M423" t="s">
         <v>35</v>
       </c>
+      <c r="N423" t="s">
+        <v>609</v>
+      </c>
       <c r="O423" t="s">
         <v>36</v>
       </c>
@@ -32813,6 +34082,9 @@
       <c r="M424" t="s">
         <v>35</v>
       </c>
+      <c r="N424" t="s">
+        <v>609</v>
+      </c>
       <c r="O424" t="s">
         <v>36</v>
       </c>
@@ -32887,6 +34159,9 @@
       <c r="M425" t="s">
         <v>35</v>
       </c>
+      <c r="N425" t="s">
+        <v>609</v>
+      </c>
       <c r="O425" t="s">
         <v>36</v>
       </c>
@@ -32961,6 +34236,9 @@
       <c r="M426" t="s">
         <v>35</v>
       </c>
+      <c r="N426" t="s">
+        <v>609</v>
+      </c>
       <c r="O426" t="s">
         <v>36</v>
       </c>
@@ -33035,6 +34313,9 @@
       <c r="M427" t="s">
         <v>46</v>
       </c>
+      <c r="N427" t="s">
+        <v>609</v>
+      </c>
       <c r="O427" t="s">
         <v>36</v>
       </c>
@@ -33106,6 +34387,9 @@
       <c r="M428" t="s">
         <v>35</v>
       </c>
+      <c r="N428" t="s">
+        <v>609</v>
+      </c>
       <c r="O428" t="s">
         <v>36</v>
       </c>
@@ -33180,6 +34464,9 @@
       <c r="M429" t="s">
         <v>46</v>
       </c>
+      <c r="N429" t="s">
+        <v>609</v>
+      </c>
       <c r="O429" t="s">
         <v>36</v>
       </c>
@@ -33251,6 +34538,9 @@
       <c r="M430" t="s">
         <v>46</v>
       </c>
+      <c r="N430" t="s">
+        <v>609</v>
+      </c>
       <c r="O430" t="s">
         <v>36</v>
       </c>
@@ -33322,6 +34612,9 @@
       <c r="M431" t="s">
         <v>46</v>
       </c>
+      <c r="N431" t="s">
+        <v>609</v>
+      </c>
       <c r="O431" t="s">
         <v>36</v>
       </c>
@@ -33393,6 +34686,9 @@
       <c r="M432" t="s">
         <v>35</v>
       </c>
+      <c r="N432" t="s">
+        <v>609</v>
+      </c>
       <c r="O432" t="s">
         <v>36</v>
       </c>
@@ -33467,6 +34763,9 @@
       <c r="M433" t="s">
         <v>35</v>
       </c>
+      <c r="N433" t="s">
+        <v>609</v>
+      </c>
       <c r="O433" t="s">
         <v>36</v>
       </c>
@@ -33538,6 +34837,9 @@
       <c r="M434" t="s">
         <v>35</v>
       </c>
+      <c r="N434" t="s">
+        <v>609</v>
+      </c>
       <c r="O434" t="s">
         <v>36</v>
       </c>
@@ -33609,6 +34911,9 @@
       <c r="M435" t="s">
         <v>85</v>
       </c>
+      <c r="N435" t="s">
+        <v>609</v>
+      </c>
       <c r="O435" t="s">
         <v>62</v>
       </c>
@@ -33680,6 +34985,9 @@
       <c r="M436" t="s">
         <v>85</v>
       </c>
+      <c r="N436" t="s">
+        <v>609</v>
+      </c>
       <c r="O436" t="s">
         <v>62</v>
       </c>
@@ -33751,6 +35059,9 @@
       <c r="M437" t="s">
         <v>46</v>
       </c>
+      <c r="N437" t="s">
+        <v>609</v>
+      </c>
       <c r="O437" t="s">
         <v>36</v>
       </c>
@@ -33822,6 +35133,9 @@
       <c r="M438" t="s">
         <v>46</v>
       </c>
+      <c r="N438" t="s">
+        <v>609</v>
+      </c>
       <c r="O438" t="s">
         <v>36</v>
       </c>
@@ -33893,6 +35207,9 @@
       <c r="M439" t="s">
         <v>46</v>
       </c>
+      <c r="N439" t="s">
+        <v>609</v>
+      </c>
       <c r="O439" t="s">
         <v>36</v>
       </c>
@@ -33964,6 +35281,9 @@
       <c r="M440" t="s">
         <v>46</v>
       </c>
+      <c r="N440" t="s">
+        <v>609</v>
+      </c>
       <c r="O440" t="s">
         <v>36</v>
       </c>
@@ -34035,6 +35355,9 @@
       <c r="M441" t="s">
         <v>46</v>
       </c>
+      <c r="N441" t="s">
+        <v>609</v>
+      </c>
       <c r="O441" t="s">
         <v>36</v>
       </c>
@@ -34106,6 +35429,9 @@
       <c r="M442" t="s">
         <v>35</v>
       </c>
+      <c r="N442" t="s">
+        <v>609</v>
+      </c>
       <c r="O442" t="s">
         <v>36</v>
       </c>
@@ -34180,6 +35506,9 @@
       <c r="M443" t="s">
         <v>35</v>
       </c>
+      <c r="N443" t="s">
+        <v>609</v>
+      </c>
       <c r="O443" t="s">
         <v>36</v>
       </c>
@@ -34254,6 +35583,9 @@
       <c r="M444" t="s">
         <v>35</v>
       </c>
+      <c r="N444" t="s">
+        <v>609</v>
+      </c>
       <c r="O444" t="s">
         <v>36</v>
       </c>
@@ -34328,6 +35660,9 @@
       <c r="M445" t="s">
         <v>85</v>
       </c>
+      <c r="N445" t="s">
+        <v>609</v>
+      </c>
       <c r="O445" t="s">
         <v>36</v>
       </c>
@@ -34399,6 +35734,9 @@
       <c r="M446" t="s">
         <v>85</v>
       </c>
+      <c r="N446" t="s">
+        <v>609</v>
+      </c>
       <c r="O446" t="s">
         <v>62</v>
       </c>
@@ -34470,6 +35808,9 @@
       <c r="M447" t="s">
         <v>85</v>
       </c>
+      <c r="N447" t="s">
+        <v>609</v>
+      </c>
       <c r="O447" t="s">
         <v>62</v>
       </c>
@@ -34541,6 +35882,9 @@
       <c r="M448" t="s">
         <v>85</v>
       </c>
+      <c r="N448" t="s">
+        <v>609</v>
+      </c>
       <c r="O448" t="s">
         <v>62</v>
       </c>
@@ -34612,6 +35956,9 @@
       <c r="M449" t="s">
         <v>35</v>
       </c>
+      <c r="N449" t="s">
+        <v>609</v>
+      </c>
       <c r="O449" t="s">
         <v>36</v>
       </c>
@@ -34686,6 +36033,9 @@
       <c r="M450" t="s">
         <v>85</v>
       </c>
+      <c r="N450" t="s">
+        <v>609</v>
+      </c>
       <c r="O450" t="s">
         <v>62</v>
       </c>
@@ -34757,6 +36107,9 @@
       <c r="M451" t="s">
         <v>85</v>
       </c>
+      <c r="N451" t="s">
+        <v>609</v>
+      </c>
       <c r="O451" t="s">
         <v>36</v>
       </c>
@@ -34828,6 +36181,9 @@
       <c r="M452" t="s">
         <v>85</v>
       </c>
+      <c r="N452" t="s">
+        <v>609</v>
+      </c>
       <c r="O452" t="s">
         <v>36</v>
       </c>
@@ -34899,6 +36255,9 @@
       <c r="M453" t="s">
         <v>85</v>
       </c>
+      <c r="N453" t="s">
+        <v>609</v>
+      </c>
       <c r="O453" t="s">
         <v>62</v>
       </c>
@@ -34970,6 +36329,9 @@
       <c r="M454" t="s">
         <v>35</v>
       </c>
+      <c r="N454" t="s">
+        <v>609</v>
+      </c>
       <c r="O454" t="s">
         <v>36</v>
       </c>
@@ -35044,6 +36406,9 @@
       <c r="M455" t="s">
         <v>35</v>
       </c>
+      <c r="N455" t="s">
+        <v>609</v>
+      </c>
       <c r="O455" t="s">
         <v>36</v>
       </c>
@@ -35118,6 +36483,9 @@
       <c r="M456" t="s">
         <v>35</v>
       </c>
+      <c r="N456" t="s">
+        <v>609</v>
+      </c>
       <c r="O456" t="s">
         <v>36</v>
       </c>
@@ -35192,6 +36560,9 @@
       <c r="M457" t="s">
         <v>35</v>
       </c>
+      <c r="N457" t="s">
+        <v>609</v>
+      </c>
       <c r="O457" t="s">
         <v>36</v>
       </c>
@@ -35266,6 +36637,9 @@
       <c r="M458" t="s">
         <v>85</v>
       </c>
+      <c r="N458" t="s">
+        <v>609</v>
+      </c>
       <c r="O458" t="s">
         <v>36</v>
       </c>
@@ -35337,6 +36711,9 @@
       <c r="M459" t="s">
         <v>85</v>
       </c>
+      <c r="N459" t="s">
+        <v>609</v>
+      </c>
       <c r="O459" t="s">
         <v>36</v>
       </c>
@@ -35408,6 +36785,9 @@
       <c r="M460" t="s">
         <v>85</v>
       </c>
+      <c r="N460" t="s">
+        <v>609</v>
+      </c>
       <c r="O460" t="s">
         <v>62</v>
       </c>
@@ -35479,6 +36859,9 @@
       <c r="M461" t="s">
         <v>85</v>
       </c>
+      <c r="N461" t="s">
+        <v>609</v>
+      </c>
       <c r="O461" t="s">
         <v>36</v>
       </c>
@@ -35550,6 +36933,9 @@
       <c r="M462" t="s">
         <v>85</v>
       </c>
+      <c r="N462" t="s">
+        <v>609</v>
+      </c>
       <c r="O462" t="s">
         <v>36</v>
       </c>
@@ -35621,6 +37007,9 @@
       <c r="M463" t="s">
         <v>85</v>
       </c>
+      <c r="N463" t="s">
+        <v>609</v>
+      </c>
       <c r="O463" t="s">
         <v>62</v>
       </c>
@@ -35692,6 +37081,9 @@
       <c r="M464" t="s">
         <v>35</v>
       </c>
+      <c r="N464" t="s">
+        <v>609</v>
+      </c>
       <c r="O464" t="s">
         <v>62</v>
       </c>
@@ -35763,6 +37155,9 @@
       <c r="M465" t="s">
         <v>35</v>
       </c>
+      <c r="N465" t="s">
+        <v>609</v>
+      </c>
       <c r="O465" t="s">
         <v>62</v>
       </c>
@@ -35834,6 +37229,9 @@
       <c r="M466" t="s">
         <v>85</v>
       </c>
+      <c r="N466" t="s">
+        <v>609</v>
+      </c>
       <c r="O466" t="s">
         <v>36</v>
       </c>
@@ -35905,6 +37303,9 @@
       <c r="M467" t="s">
         <v>85</v>
       </c>
+      <c r="N467" t="s">
+        <v>609</v>
+      </c>
       <c r="O467" t="s">
         <v>62</v>
       </c>
@@ -35976,6 +37377,9 @@
       <c r="M468" t="s">
         <v>85</v>
       </c>
+      <c r="N468" t="s">
+        <v>609</v>
+      </c>
       <c r="O468" t="s">
         <v>36</v>
       </c>
@@ -36047,6 +37451,9 @@
       <c r="M469" t="s">
         <v>85</v>
       </c>
+      <c r="N469" t="s">
+        <v>609</v>
+      </c>
       <c r="O469" t="s">
         <v>36</v>
       </c>
@@ -36118,6 +37525,9 @@
       <c r="M470" t="s">
         <v>46</v>
       </c>
+      <c r="N470" t="s">
+        <v>609</v>
+      </c>
       <c r="O470" t="s">
         <v>36</v>
       </c>
@@ -36189,6 +37599,9 @@
       <c r="M471" t="s">
         <v>85</v>
       </c>
+      <c r="N471" t="s">
+        <v>609</v>
+      </c>
       <c r="O471" t="s">
         <v>36</v>
       </c>
@@ -36260,6 +37673,9 @@
       <c r="M472" t="s">
         <v>85</v>
       </c>
+      <c r="N472" t="s">
+        <v>609</v>
+      </c>
       <c r="O472" t="s">
         <v>62</v>
       </c>
@@ -36331,6 +37747,9 @@
       <c r="M473" t="s">
         <v>35</v>
       </c>
+      <c r="N473" t="s">
+        <v>609</v>
+      </c>
       <c r="O473" t="s">
         <v>62</v>
       </c>
@@ -36402,6 +37821,9 @@
       <c r="M474" t="s">
         <v>35</v>
       </c>
+      <c r="N474" t="s">
+        <v>609</v>
+      </c>
       <c r="O474" t="s">
         <v>62</v>
       </c>
@@ -36473,6 +37895,9 @@
       <c r="M475" t="s">
         <v>35</v>
       </c>
+      <c r="N475" t="s">
+        <v>609</v>
+      </c>
       <c r="O475" t="s">
         <v>62</v>
       </c>
@@ -36544,6 +37969,9 @@
       <c r="M476" t="s">
         <v>35</v>
       </c>
+      <c r="N476" t="s">
+        <v>609</v>
+      </c>
       <c r="O476" t="s">
         <v>62</v>
       </c>
@@ -36615,6 +38043,9 @@
       <c r="M477" t="s">
         <v>35</v>
       </c>
+      <c r="N477" t="s">
+        <v>609</v>
+      </c>
       <c r="O477" t="s">
         <v>62</v>
       </c>
@@ -36689,6 +38120,9 @@
       <c r="M478" t="s">
         <v>35</v>
       </c>
+      <c r="N478" t="s">
+        <v>609</v>
+      </c>
       <c r="O478" t="s">
         <v>62</v>
       </c>
@@ -36763,6 +38197,9 @@
       <c r="M479" t="s">
         <v>35</v>
       </c>
+      <c r="N479" t="s">
+        <v>609</v>
+      </c>
       <c r="O479" t="s">
         <v>62</v>
       </c>
@@ -36834,6 +38271,9 @@
       <c r="M480" t="s">
         <v>35</v>
       </c>
+      <c r="N480" t="s">
+        <v>609</v>
+      </c>
       <c r="O480" t="s">
         <v>62</v>
       </c>
@@ -36908,6 +38348,9 @@
       <c r="M481" t="s">
         <v>35</v>
       </c>
+      <c r="N481" t="s">
+        <v>609</v>
+      </c>
       <c r="O481" t="s">
         <v>62</v>
       </c>
@@ -36982,6 +38425,9 @@
       <c r="M482" t="s">
         <v>35</v>
       </c>
+      <c r="N482" t="s">
+        <v>609</v>
+      </c>
       <c r="O482" t="s">
         <v>62</v>
       </c>
@@ -37053,6 +38499,9 @@
       <c r="M483" t="s">
         <v>35</v>
       </c>
+      <c r="N483" t="s">
+        <v>609</v>
+      </c>
       <c r="O483" t="s">
         <v>62</v>
       </c>
@@ -37127,6 +38576,9 @@
       <c r="M484" t="s">
         <v>85</v>
       </c>
+      <c r="N484" t="s">
+        <v>609</v>
+      </c>
       <c r="O484" t="s">
         <v>62</v>
       </c>
@@ -37198,6 +38650,9 @@
       <c r="M485" t="s">
         <v>85</v>
       </c>
+      <c r="N485" t="s">
+        <v>609</v>
+      </c>
       <c r="O485" t="s">
         <v>62</v>
       </c>
@@ -37269,6 +38724,9 @@
       <c r="M486" t="s">
         <v>46</v>
       </c>
+      <c r="N486" t="s">
+        <v>609</v>
+      </c>
       <c r="O486" t="s">
         <v>62</v>
       </c>
@@ -37340,6 +38798,9 @@
       <c r="M487" t="s">
         <v>35</v>
       </c>
+      <c r="N487" t="s">
+        <v>609</v>
+      </c>
       <c r="O487" t="s">
         <v>62</v>
       </c>
@@ -37414,6 +38875,9 @@
       <c r="M488" t="s">
         <v>35</v>
       </c>
+      <c r="N488" t="s">
+        <v>609</v>
+      </c>
       <c r="O488" t="s">
         <v>36</v>
       </c>
@@ -37485,6 +38949,9 @@
       <c r="M489" t="s">
         <v>35</v>
       </c>
+      <c r="N489" t="s">
+        <v>609</v>
+      </c>
       <c r="O489" t="s">
         <v>36</v>
       </c>
@@ -37556,6 +39023,9 @@
       <c r="M490" t="s">
         <v>35</v>
       </c>
+      <c r="N490" t="s">
+        <v>609</v>
+      </c>
       <c r="O490" t="s">
         <v>62</v>
       </c>
@@ -37630,6 +39100,9 @@
       <c r="M491" t="s">
         <v>35</v>
       </c>
+      <c r="N491" t="s">
+        <v>609</v>
+      </c>
       <c r="O491" t="s">
         <v>62</v>
       </c>
@@ -37704,6 +39177,9 @@
       <c r="M492" t="s">
         <v>35</v>
       </c>
+      <c r="N492" t="s">
+        <v>609</v>
+      </c>
       <c r="O492" t="s">
         <v>36</v>
       </c>
@@ -37777,6 +39253,9 @@
       </c>
       <c r="M493" t="s">
         <v>35</v>
+      </c>
+      <c r="N493" t="s">
+        <v>609</v>
       </c>
       <c r="O493" t="s">
         <v>36</v>
@@ -37836,20 +39315,20 @@
   <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="36.42" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="29.421" customWidth="true" style="0"/>
+    <col min="2" max="2" width="18.71" customWidth="true" style="0"/>
+    <col min="3" max="3" width="36.42" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.425" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" customWidth="true" style="0"/>
+    <col min="6" max="6" width="15.282" customWidth="true" style="0"/>
+    <col min="7" max="7" width="30.564" customWidth="true" style="0"/>
+    <col min="8" max="8" width="39.99" customWidth="true" style="0"/>
+    <col min="9" max="9" width="31.707" customWidth="true" style="0"/>
+    <col min="10" max="10" width="16.425" customWidth="true" style="0"/>
+    <col min="11" max="11" width="9.283" customWidth="true" style="0"/>
+    <col min="12" max="12" width="22.28" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="22.28" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -37898,13 +39377,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -37925,16 +39404,16 @@
         <v>227</v>
       </c>
       <c r="J2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N2" t="s">
         <v>66</v>
@@ -37942,19 +39421,19 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F3" t="s">
         <v>36</v>
@@ -37963,7 +39442,7 @@
         <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I3" t="s">
         <v>264</v>
@@ -37989,10 +39468,10 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D4" t="s">
         <v>85</v>
@@ -38004,7 +39483,7 @@
         <v>342</v>
       </c>
       <c r="H4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="I4" t="s">
         <v>173</v>
@@ -38015,19 +39494,19 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E5" t="s">
         <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I5" t="s">
         <v>233</v>
@@ -38035,16 +39514,16 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B6" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E6" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I6" t="s">
         <v>86</v>
@@ -38052,13 +39531,13 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I7" t="s">
         <v>243</v>
@@ -38066,13 +39545,13 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I8" t="s">
         <v>183</v>
@@ -38080,10 +39559,10 @@
     </row>
     <row r="9" spans="1:14">
       <c r="B9" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H9" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I9" t="s">
         <v>307</v>
@@ -38091,10 +39570,10 @@
     </row>
     <row r="10" spans="1:14">
       <c r="B10" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I10" t="s">
         <v>155</v>
@@ -38102,10 +39581,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H11" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I11" t="s">
         <v>319</v>
@@ -38116,7 +39595,7 @@
         <v>33</v>
       </c>
       <c r="H12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I12" t="s">
         <v>252</v>
@@ -38124,10 +39603,10 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I13" t="s">
         <v>224</v>
@@ -38135,7 +39614,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="H14" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I14" t="s">
         <v>222</v>
@@ -38143,7 +39622,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="H15" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I15" t="s">
         <v>422</v>
@@ -38151,7 +39630,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="H16" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I16" t="s">
         <v>325</v>
@@ -38159,7 +39638,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="H17" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I17" t="s">
         <v>246</v>
@@ -38167,7 +39646,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="H18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I18" t="s">
         <v>165</v>
@@ -38175,7 +39654,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="H19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I19" t="s">
         <v>486</v>
@@ -38298,7 +39777,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="I43" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
